--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,7 +13,7 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$30:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$163</definedName>
   </definedNames>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2991,8 +2991,45 @@
       </c>
       <c r="G70" s="3" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>NFR-043</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>계좌 동시성 정합성</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>동시 계좌 개설(같은/다른 Idempotency-Key), 동시 대표 계좌 변경 후 확인: 대표 계좌 항상 1개, 멱등키 재사용 시 신규 계좌 미생성. 실제 PostgreSQL(Testcontainers)로 검증(목·가짜 DB 사용 안 함)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>E-03, E-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3654,7 +3691,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>첫 계좌면 대표</t>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
         </is>
       </c>
     </row>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$30:$H$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4301,7 +4301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4704,17 +4704,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>Header Idempotency-Key</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>재시도 판별용 클라이언트 생성 키(UUID)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3f2504e0-4f89-4...</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12자리 자동 발급</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>12자리 자동 발급</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.balance</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4835,12 +4835,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부(첫 계좌면 true)</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4852,59 +4852,59 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부(첫 계좌면 true)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountNumber</t>
+          <t>data.accounts[].accountId</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].balance</t>
+          <t>data.accounts[].accountNumber</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].primary</t>
+          <t>data.accounts[].balance</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
@@ -5062,59 +5062,59 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>data.accounts[].primary</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>대표로 바꿀 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>대표로 바꿀 계좌 ID</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -5235,22 +5235,34 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5265,14 +5277,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -5290,14 +5302,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -5305,39 +5317,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>충전할 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>충전 금액(원)</t>
+          <t>충전할 계좌 ID</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5421,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>충전 금액(원)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>충전 후 잔액(원)</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5495,22 +5495,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>data.balance</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>충전 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5525,14 +5537,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5550,14 +5562,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5565,39 +5577,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>accountNumber</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5681,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>data.aliasId</t>
+          <t>accountNumber</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>상대 계좌번호</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5723,12 +5723,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>data.alias</t>
+          <t>data.aliasId</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.alias</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>data.ownerName</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5829,22 +5829,34 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>data.ownerName</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5859,14 +5871,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -5874,39 +5886,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].aliasId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].alias</t>
+          <t>data.aliases[].aliasId</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].accountNumber</t>
+          <t>data.aliases[].alias</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].ownerName</t>
+          <t>data.aliases[].accountNumber</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6064,59 +6064,59 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>data.aliases[].ownerName</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6131,27 +6131,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6168,12 +6168,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>묶음 크기(기본 20)</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -6200,32 +6200,32 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6353,12 +6353,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6427,27 +6427,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -6464,27 +6464,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -6496,59 +6496,59 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>data.threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Spring이 발급, 사용자와 묶어 저장</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6595,59 +6595,59 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>data.threadId</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Spring이 발급, 사용자와 묶어 저장</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>th_5b21...</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Path threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>대화 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Path threadId</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6820,17 +6820,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -7175,22 +7175,34 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7205,14 +7217,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -7230,14 +7242,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
@@ -7255,14 +7267,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>RATE_LIMITED</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>사용자별 채팅 호출 제한 초과</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -7270,39 +7282,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Path requestId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>확인 카드의 요청ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7349,17 +7349,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>data.transferId</t>
+          <t>Path requestId</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>확인 카드의 요청ID</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -7391,12 +7391,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.transferId</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>data.balanceAfter</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>송금 후 잔액(원)</t>
+          <t>출금 계좌</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -7534,22 +7534,34 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>data.balanceAfter</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
+          <t>송금 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7564,14 +7576,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
@@ -7589,14 +7601,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -7614,14 +7626,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -7639,14 +7651,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>이미 확정된 송금 요청</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -7664,14 +7676,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>ACCOUNT_NOT_OWNED</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>내 계좌가 아님</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -7679,39 +7691,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INSUFFICIENT_BALANCE</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>잔액 부족</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>답변의 detailId</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>답변의 detailId</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문(클릭할 때 생성)</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -7837,27 +7837,27 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문(클릭할 때 생성)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -7911,12 +7911,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -7943,22 +7943,34 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7973,14 +7985,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -7998,14 +8010,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>DETAIL_NOT_FOUND</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
@@ -8013,39 +8025,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -8297,12 +8297,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8393,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -8573,59 +8573,59 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr"/>
-      <c r="E125" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8714,27 +8714,27 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8788,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -8820,22 +8820,34 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8850,14 +8862,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
@@ -8865,39 +8877,27 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8986,27 +8986,27 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9018,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.requestId</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9075,12 +9075,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9112,12 +9112,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9171,12 +9171,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -9208,12 +9208,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9240,22 +9240,34 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
+          <t>data.expiresAt</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9270,14 +9282,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
@@ -9295,14 +9307,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>ALIAS_NOT_FOUND</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>등록되지 않은 별칭</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -9310,39 +9322,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
+          <t>Query from</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
+          <t>시작일(yyyy-MM-dd)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9431,25 +9431,29 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Query to</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
+          <t>종료일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9464,12 +9468,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -9479,14 +9483,10 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9496,32 +9496,32 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>기본 20</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>data.sentTotal</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
@@ -9575,12 +9575,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>data.receivedTotal</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -9612,12 +9612,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.count</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>기간 내 건수</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9797,12 +9797,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9812,12 +9812,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9834,27 +9834,27 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -9871,27 +9871,27 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -9903,25 +9903,62 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr"/>
-      <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G163"/>
+  <autoFilter ref="A1:G164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,9 +13,9 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$30:$H$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2991,8 +2991,45 @@
       </c>
       <c r="G70" s="3" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>NFR-043</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>계좌 동시성 정합성</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>동시 계좌 개설(같은/다른 Idempotency-Key), 동시 대표 계좌 변경 후 확인: 대표 계좌 항상 1개, 멱등키 재사용 시 신규 계좌 미생성. 실제 PostgreSQL(Testcontainers)로 검증(목·가짜 DB 사용 안 함)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>E-03, E-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3654,7 +3691,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>첫 계좌면 대표</t>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4667,17 +4704,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>Header Idempotency-Key</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4687,12 +4724,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>재시도 판별용 클라이언트 생성 키(UUID)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3f2504e0-4f89-4...</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4746,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4724,12 +4761,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12자리 자동 발급</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4783,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4761,12 +4798,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>12자리 자동 발급</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4820,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.balance</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4798,12 +4835,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부(첫 계좌면 true)</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4815,59 +4852,59 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부(첫 계좌면 true)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4877,17 +4914,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4897,12 +4934,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4956,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountNumber</t>
+          <t>data.accounts[].accountId</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4934,12 +4971,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4993,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].balance</t>
+          <t>data.accounts[].accountNumber</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4971,12 +5008,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -4993,12 +5030,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].primary</t>
+          <t>data.accounts[].balance</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -5008,12 +5045,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
@@ -5025,59 +5062,59 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>data.accounts[].primary</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5092,12 +5129,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5107,12 +5144,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>대표로 바꿀 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5161,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5144,7 +5181,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>대표로 바꿀 계좌 ID</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5166,12 +5203,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5181,12 +5218,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -5198,22 +5235,34 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5228,14 +5277,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -5253,14 +5302,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -5268,39 +5317,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5315,12 +5352,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -5330,12 +5367,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>충전할 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5389,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5367,12 +5404,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>충전 금액(원)</t>
+          <t>충전할 계좌 ID</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5421,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5404,12 +5441,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>충전 금액(원)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5463,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5441,12 +5478,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>충전 후 잔액(원)</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5458,22 +5495,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>data.balance</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>충전 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5488,14 +5537,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5513,14 +5562,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5528,39 +5577,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5575,7 +5612,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5590,12 +5627,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5649,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>accountNumber</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5627,12 +5664,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5644,17 +5681,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>data.aliasId</t>
+          <t>accountNumber</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5664,12 +5701,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>상대 계좌번호</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5723,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>data.alias</t>
+          <t>data.aliasId</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5701,12 +5738,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5760,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.alias</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5738,12 +5775,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5797,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>data.ownerName</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5775,12 +5812,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5792,22 +5829,34 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>data.ownerName</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5822,14 +5871,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -5837,39 +5886,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5879,17 +5916,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].aliasId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5899,12 +5936,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5921,12 +5958,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].alias</t>
+          <t>data.aliases[].aliasId</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5936,12 +5973,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5995,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].accountNumber</t>
+          <t>data.aliases[].alias</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -5973,12 +6010,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6032,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].ownerName</t>
+          <t>data.aliases[].accountNumber</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6010,12 +6047,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6027,59 +6064,59 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>data.aliases[].ownerName</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6094,27 +6131,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6131,12 +6168,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6146,12 +6183,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>묶음 크기(기본 20)</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -6163,32 +6200,32 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6242,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6220,12 +6257,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6279,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -6257,12 +6294,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6316,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -6294,12 +6331,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6353,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -6331,12 +6368,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6353,12 +6390,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6368,12 +6405,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6390,27 +6427,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -6427,27 +6464,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -6459,59 +6496,59 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6521,12 +6558,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>data.threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6541,12 +6578,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Spring이 발급, 사용자와 묶어 저장</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6558,59 +6595,59 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>data.threadId</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Spring이 발급, 사용자와 묶어 저장</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>th_5b21...</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6625,7 +6662,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Path threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6640,12 +6677,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>대화 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6699,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Path threadId</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6677,12 +6714,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -6694,12 +6731,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -6714,12 +6751,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6773,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6751,12 +6788,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6810,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6783,17 +6820,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6847,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6825,12 +6862,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6884,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6862,12 +6899,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6921,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6899,12 +6936,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6921,12 +6958,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6936,12 +6973,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6995,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6973,12 +7010,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6995,12 +7032,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7010,12 +7047,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7069,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7047,12 +7084,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7106,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7084,12 +7121,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7143,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7121,12 +7158,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -7138,22 +7175,34 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7168,14 +7217,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -7193,14 +7242,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
@@ -7218,14 +7267,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>RATE_LIMITED</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>사용자별 채팅 호출 제한 초과</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -7233,39 +7282,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7280,7 +7317,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Path requestId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7295,12 +7332,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>확인 카드의 요청ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7312,17 +7349,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>data.transferId</t>
+          <t>Path requestId</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7332,12 +7369,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>확인 카드의 요청ID</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7391,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.transferId</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7369,12 +7406,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -7391,12 +7428,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7406,12 +7443,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7465,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7443,12 +7480,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7502,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>data.balanceAfter</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7480,12 +7517,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>송금 후 잔액(원)</t>
+          <t>출금 계좌</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -7497,22 +7534,34 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>data.balanceAfter</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
+          <t>송금 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7527,14 +7576,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
@@ -7552,14 +7601,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -7577,14 +7626,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -7602,14 +7651,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>이미 확정된 송금 요청</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -7627,14 +7676,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>ACCOUNT_NOT_OWNED</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>내 계좌가 아님</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -7642,39 +7691,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INSUFFICIENT_BALANCE</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>잔액 부족</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7689,7 +7726,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -7704,12 +7741,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>답변의 detailId</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7758,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7741,7 +7778,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>답변의 detailId</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -7763,7 +7800,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7778,12 +7815,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문(클릭할 때 생성)</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -7800,27 +7837,27 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문(클릭할 때 생성)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7837,12 +7874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7852,12 +7889,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7911,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7889,12 +7926,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -7906,22 +7943,34 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7936,14 +7985,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -7961,14 +8010,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>DETAIL_NOT_FOUND</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
@@ -7976,39 +8025,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8023,7 +8060,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8038,12 +8075,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8097,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8075,12 +8112,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -8092,12 +8129,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8112,12 +8149,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8171,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8149,12 +8186,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8208,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -8181,17 +8218,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8245,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8223,12 +8260,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8282,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -8260,12 +8297,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8319,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -8297,12 +8334,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8319,12 +8356,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8334,12 +8371,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8393,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8371,12 +8408,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8430,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8408,12 +8445,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8467,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8445,12 +8482,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8504,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8482,12 +8519,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8541,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -8519,12 +8556,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -8536,59 +8573,59 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr"/>
-      <c r="E125" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8603,7 +8640,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -8618,12 +8655,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8635,12 +8672,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -8655,12 +8692,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8677,27 +8714,27 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8751,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8729,12 +8766,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8788,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -8766,12 +8803,12 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -8783,22 +8820,34 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8813,14 +8862,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
@@ -8828,39 +8877,27 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8875,7 +8912,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -8885,17 +8922,17 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8949,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8927,12 +8964,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8949,27 +8986,27 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -8981,17 +9018,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -9001,12 +9038,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9060,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.requestId</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9038,12 +9075,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9097,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9075,12 +9112,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9134,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9112,12 +9149,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9171,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9149,12 +9186,12 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -9171,12 +9208,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9186,12 +9223,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9203,22 +9240,34 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
+          <t>data.expiresAt</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9233,14 +9282,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
@@ -9258,14 +9307,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>ALIAS_NOT_FOUND</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>등록되지 않은 별칭</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -9273,39 +9322,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9320,7 +9357,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9335,12 +9372,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9394,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
+          <t>Query from</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9372,12 +9409,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
+          <t>시작일(yyyy-MM-dd)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9394,25 +9431,29 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Query to</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
+          <t>종료일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9427,12 +9468,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -9442,14 +9483,10 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9459,32 +9496,32 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>기본 20</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9538,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>data.sentTotal</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -9516,12 +9553,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
@@ -9538,12 +9575,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>data.receivedTotal</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -9553,12 +9590,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -9575,12 +9612,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.count</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -9590,12 +9627,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>기간 내 건수</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -9612,12 +9649,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9627,12 +9664,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9686,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -9664,12 +9701,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9723,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -9701,12 +9738,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9760,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9738,12 +9775,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9760,12 +9797,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9775,12 +9812,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9797,27 +9834,27 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -9834,27 +9871,27 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -9866,25 +9903,62 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr"/>
-      <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G163"/>
+  <autoFilter ref="A1:G164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$30:$H$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$31:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3040,7 +3040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3250,15 +3250,15 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>INVALID_AMOUNT</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>충전 금액이 0 이하</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -3270,15 +3270,15 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
+          <t>INSUFFICIENT_BALANCE</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
+          <t>잔액 부족</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -3290,7 +3290,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
+          <t>ALIAS_NOT_FOUND</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
+          <t>등록되지 않은 별칭</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
@@ -3310,15 +3310,15 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -3330,15 +3330,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
@@ -3350,15 +3350,15 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>이미 확정된 송금 요청</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -3390,15 +3390,15 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>DETAIL_NOT_FOUND</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>503</v>
+        <v>404</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -3410,15 +3410,15 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>AI_SERVER_UNAVAILABLE</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>429</v>
+        <v>503</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -3428,17 +3428,19 @@
       <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>guard 코드</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RATE_LIMITED</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>사용자별 채팅 호출 제한 초과</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -3446,14 +3448,14 @@
       <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>통과</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>guard 코드</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>설명</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -3466,12 +3468,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>INJECTION</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -3484,12 +3486,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NUMBER_UNVERIFIED</t>
+          <t>INJECTION</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
+          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -3502,12 +3504,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ADVICE</t>
+          <t>NUMBER_UNVERIFIED</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 투자 권유 표현</t>
+          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
@@ -3520,12 +3522,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PROMPT_LEAK</t>
+          <t>ADVICE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+          <t>출력 교체 — 투자 권유 표현</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -3535,90 +3537,71 @@
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="10" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>PROMPT_LEAK</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>API ID</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/auth/signup</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>회원가입</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>FR-001</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3633,12 +3616,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/signup</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>회원가입</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3648,7 +3631,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>FR-002</t>
+          <t>FR-001</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -3656,7 +3639,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3671,34 +3654,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>가상계좌 개설</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Bearer</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>FR-003, FR-004</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
-        </is>
-      </c>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3708,7 +3687,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3718,7 +3697,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>내 계좌·잔액 조회</t>
+          <t>가상계좌 개설</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3728,15 +3707,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>FR-003, FR-004</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3746,17 +3729,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/primary</t>
+          <t>/api/v1/accounts</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 변경</t>
+          <t>내 계좌·잔액 조회</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3766,7 +3749,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>FR-004</t>
+          <t>FR-006</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -3774,7 +3757,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3784,17 +3767,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/charge</t>
+          <t>/api/v1/accounts/{accountId}/primary</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>충전</t>
+          <t>대표 계좌 변경</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3804,7 +3787,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>FR-005</t>
+          <t>FR-004</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -3812,7 +3795,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3827,12 +3810,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/aliases</t>
+          <t>/api/v1/accounts/{accountId}/charge</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>별칭 등록</t>
+          <t>충전</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3842,7 +3825,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>FR-007</t>
+          <t>FR-005</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -3850,7 +3833,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3860,7 +3843,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3870,7 +3853,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>별칭 목록</t>
+          <t>별칭 등록</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3880,7 +3863,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>FR-008</t>
+          <t>FR-007</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -3888,7 +3871,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3903,12 +3886,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfers?cursor&amp;size</t>
+          <t>/api/v1/aliases</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록</t>
+          <t>별칭 목록</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3918,19 +3901,15 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>FR-011</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
-        </is>
-      </c>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3940,17 +3919,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads</t>
+          <t>/api/v1/transfers?cursor&amp;size</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>새 대화</t>
+          <t>송금 내역 목록</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3960,15 +3939,19 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>FR-013</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>FR-011</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3983,12 +3966,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads/{threadId}/messages</t>
+          <t>/api/v1/chat/threads</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지</t>
+          <t>새 대화</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3998,19 +3981,15 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Spring이 I-01 호출. 호출 제한 적용</t>
-        </is>
-      </c>
+          <t>FR-013</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4025,12 +4004,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
+          <t>/api/v1/chat/threads/{threadId}/messages</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>송금 확정([보내기])</t>
+          <t>채팅 메시지</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4040,19 +4019,19 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>FR-010, NFR-001, NFR-009, NFR-010</t>
+          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>AI 경로를 거치지 않음</t>
+          <t>Spring이 I-01 호출. 호출 제한 적용</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4062,17 +4041,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/details/{detailId}</t>
+          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>송금 확정([보내기])</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4082,61 +4061,61 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>FR-016, FR-019</t>
+          <t>FR-010, NFR-001, NFR-009, NFR-010</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Spring이 I-02 호출</t>
+          <t>AI 경로를 거치지 않음</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>/internal/chat</t>
+          <t>/api/v1/chat/details/{detailId}</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>채팅 처리(LangGraph 구동)</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, NFR-005, NFR-006</t>
+          <t>FR-016, FR-019</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>Spring이 I-02 호출</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -4146,17 +4125,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>/internal/details/{detailId}</t>
+          <t>/internal/chat</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 생성</t>
+          <t>채팅 처리(LangGraph 구동)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -4166,7 +4145,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>FR-016, NFR-005, NFR-006</t>
+          <t>FR-014, FR-015, NFR-005, NFR-006</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -4178,27 +4157,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>내부 FastAPI→Spring</t>
+          <t>내부 Spring→FastAPI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/internal/transfer-requests</t>
+          <t>/internal/details/{detailId}</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 생성(확인 카드용)</t>
+          <t>상세 보고서 생성</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4208,59 +4187,101 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+          <t>FR-016, NFR-005, NFR-006</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 도구. 실행은 하지 않음</t>
+          <t>FastAPI 쪽 API</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>내부 FastAPI→Spring</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>/internal/transfer-requests</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청 생성(확인 카드용)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph 도구. 실행은 하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>내부 FastAPI→Spring</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>/internal/transfers?from&amp;to&amp;cursor&amp;size</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>송금 내역·합계 조회</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Bearer(사용자 JWT 전달)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>FR-012, NFR-002, NFR-005, NFR-006</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>LangGraph 도구. 합계는 Spring 계산</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A30:H47"/>
+  <autoFilter ref="A31:H48"/>
   <mergeCells count="28">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -4301,7 +4322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5602,39 +5623,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INVALID_AMOUNT</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>충전 금액이 0 이하</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5649,7 +5658,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5664,12 +5673,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5695,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>accountNumber</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5701,12 +5710,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5727,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>data.aliasId</t>
+          <t>accountNumber</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5738,12 +5747,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>상대 계좌번호</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5760,12 +5769,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>data.alias</t>
+          <t>data.aliasId</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5775,12 +5784,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5806,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.alias</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5812,12 +5821,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5843,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>data.ownerName</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5849,12 +5858,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5866,22 +5875,34 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>data.ownerName</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5896,14 +5917,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -5911,39 +5932,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5953,17 +5962,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].aliasId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5973,12 +5982,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5995,12 +6004,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].alias</t>
+          <t>data.aliases[].aliasId</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6010,12 +6019,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6041,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].accountNumber</t>
+          <t>data.aliases[].alias</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6047,12 +6056,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6078,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].ownerName</t>
+          <t>data.aliases[].accountNumber</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6084,12 +6093,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6101,59 +6110,59 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>data.aliases[].ownerName</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -6168,27 +6177,27 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6214,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6220,12 +6229,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>묶음 크기(기본 20)</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -6237,32 +6246,32 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6288,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6294,12 +6303,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6325,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -6331,12 +6340,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6362,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -6368,12 +6377,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6399,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6405,12 +6414,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6436,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6442,12 +6451,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6464,27 +6473,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -6501,27 +6510,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -6533,59 +6542,59 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6595,12 +6604,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>data.threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -6615,12 +6624,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Spring이 발급, 사용자와 묶어 저장</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6632,59 +6641,59 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>data.threadId</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>Spring이 발급, 사용자와 묶어 저장</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>th_5b21...</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6699,7 +6708,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Path threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6714,12 +6723,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>대화 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6745,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Path threadId</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -6751,12 +6760,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -6768,12 +6777,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6788,12 +6797,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6819,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6825,12 +6834,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6856,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6857,17 +6866,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6893,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6899,12 +6908,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6930,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6936,12 +6945,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6967,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6973,12 +6982,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6995,12 +7004,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7010,12 +7019,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7041,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7047,12 +7056,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7078,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7084,12 +7093,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7115,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7121,12 +7130,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7152,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7158,12 +7167,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7189,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -7195,12 +7204,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -7212,22 +7221,34 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7242,14 +7263,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
@@ -7267,14 +7288,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -7292,14 +7313,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>RATE_LIMITED</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>사용자별 채팅 호출 제한 초과</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
@@ -7307,39 +7328,27 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7354,7 +7363,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Path requestId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7369,12 +7378,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>확인 카드의 요청ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7386,17 +7395,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>data.transferId</t>
+          <t>Path requestId</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7406,12 +7415,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>확인 카드의 요청ID</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7437,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.transferId</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7443,12 +7452,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7474,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7480,12 +7489,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -7502,12 +7511,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7517,12 +7526,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7539,12 +7548,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>data.balanceAfter</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7554,12 +7563,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>송금 후 잔액(원)</t>
+          <t>출금 계좌</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -7571,22 +7580,34 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>data.balanceAfter</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
+          <t>송금 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7601,14 +7622,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -7626,14 +7647,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -7651,14 +7672,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -7676,14 +7697,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>이미 확정된 송금 요청</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -7701,14 +7722,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>ACCOUNT_NOT_OWNED</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>내 계좌가 아님</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -7716,39 +7737,27 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INSUFFICIENT_BALANCE</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>잔액 부족</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7763,7 +7772,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7778,12 +7787,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>답변의 detailId</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7804,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7815,7 +7824,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>답변의 detailId</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -7837,7 +7846,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -7852,12 +7861,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문(클릭할 때 생성)</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -7874,27 +7883,27 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문(클릭할 때 생성)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -7911,12 +7920,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7926,12 +7935,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7957,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -7963,12 +7972,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -7980,22 +7989,34 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -8010,14 +8031,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
@@ -8035,14 +8056,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>DETAIL_NOT_FOUND</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -8050,39 +8071,27 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8097,7 +8106,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8112,12 +8121,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8143,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8149,12 +8158,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -8166,12 +8175,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8186,12 +8195,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8217,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -8223,12 +8232,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8254,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8255,17 +8264,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8291,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -8297,12 +8306,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8328,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -8334,12 +8343,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8365,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -8371,12 +8380,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8402,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8408,12 +8417,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8439,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8445,12 +8454,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8476,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8482,12 +8491,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8513,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8519,12 +8528,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -8541,12 +8550,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -8556,12 +8565,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8587,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -8593,12 +8602,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -8610,59 +8619,59 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8677,7 +8686,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -8692,12 +8701,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8718,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -8729,12 +8738,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8751,27 +8760,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보고서 본문</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8797,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -8803,12 +8812,12 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8834,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -8840,12 +8849,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
@@ -8857,22 +8866,34 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8887,14 +8908,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
@@ -8902,39 +8923,27 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8949,7 +8958,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8959,17 +8968,17 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8995,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -9001,12 +9010,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9023,27 +9032,27 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -9055,17 +9064,17 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -9075,12 +9084,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9106,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.requestId</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9112,12 +9121,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9143,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9149,12 +9158,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9180,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -9186,12 +9195,12 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9208,12 +9217,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9223,12 +9232,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -9245,12 +9254,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9260,12 +9269,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9277,22 +9286,34 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
+          <t>data.expiresAt</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr"/>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9307,14 +9328,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -9332,14 +9353,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>ALIAS_NOT_FOUND</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>등록되지 않은 별칭</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
@@ -9347,39 +9368,27 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9394,7 +9403,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9409,12 +9418,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9440,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
+          <t>Query from</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -9446,12 +9455,12 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
+          <t>시작일(yyyy-MM-dd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9468,25 +9477,29 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Query to</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr"/>
+          <t>종료일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9501,12 +9514,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -9516,14 +9529,10 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9533,32 +9542,32 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>기본 20</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9584,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>data.sentTotal</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -9590,12 +9599,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
@@ -9612,12 +9621,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>data.receivedTotal</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -9627,12 +9636,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -9649,12 +9658,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.count</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9664,12 +9673,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>기간 내 건수</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -9686,12 +9695,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -9701,12 +9710,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9732,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -9738,12 +9747,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9769,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -9775,12 +9784,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9797,12 +9806,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9812,12 +9821,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9843,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -9849,12 +9858,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9871,27 +9880,27 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -9908,27 +9917,27 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -9940,25 +9949,62 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G164"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 제한 값 미정. 초과 시 HTTP 429 RATE_LIMITED</t>
+          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3436,11 +3436,7 @@
       <c r="B23" s="2" t="n">
         <v>429</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
-        </is>
-      </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -3555,7 +3551,6 @@
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -3436,7 +3436,11 @@
       <c r="B23" s="2" t="n">
         <v>429</v>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>사용자별 채팅 호출 제한 초과</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -3551,6 +3555,7 @@
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>서버가 12자리 숫자를 중복 없이 자동 발급. 한 사용자가 여러 개 보유 가능</t>
+          <t>서버가 12자리 숫자를 중복 없이 자동 발급. 한 사용자가 여러 개 보유 가능. 개설할 때 계좌 비밀번호(숫자 4자리)를 정하고 해시로 저장</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[보내기] → 요청ID로 확정. 1회용, 5분 만료, 계좌 소유자 확인. 잔액 차감·입금·내역 기록을 트랜잭션 하나로 처리. 받은 쪽 잔액 증가</t>
+          <t>[보내기] → 요청ID와 출금 계좌 비밀번호로 확정. 1회용, 5분 만료, 계좌 소유자 확인. 비밀번호가 틀리면 송금하지 않고 요청ID를 폐기(채팅으로 다시 요청). 비밀번호는 확인 카드에서만 받고 채팅·AI 경로로는 받지 않음. 잔액 차감·입금·내역 기록을 트랜잭션 하나로 처리. 받은 쪽 잔액 증가</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>송금 PIN·한도</t>
+          <t>송금 한도·비밀번호 연속 오류 잠금</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>송금 금액·수취인을 스키마로 검증하고 원문과 다시 대조. 애매하면 되묻기</t>
+          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3250,15 +3250,15 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INVALID_AMOUNT</t>
+          <t>ACCOUNT_PASSWORD_INVALID</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>충전 금액이 0 이하</t>
+          <t>계좌 비밀번호 불일치 — 송금 요청ID도 폐기</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -3270,15 +3270,15 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>INVALID_AMOUNT</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>충전 금액이 0 이하</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -3290,15 +3290,15 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
+          <t>INSUFFICIENT_BALANCE</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
+          <t>잔액 부족</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
@@ -3310,7 +3310,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
+          <t>ALIAS_NOT_FOUND</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
+          <t>등록되지 않은 별칭</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -3330,15 +3330,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
@@ -3350,15 +3350,15 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -3370,15 +3370,15 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>이미 쓴 송금 요청(확정됨 또는 비밀번호 오류로 폐기)</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -3390,7 +3390,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -3410,15 +3410,15 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>DETAIL_NOT_FOUND</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>503</v>
+        <v>404</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -3430,15 +3430,15 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>AI_SERVER_UNAVAILABLE</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>429</v>
+        <v>503</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -3448,17 +3448,19 @@
       <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>guard 코드</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RATE_LIMITED</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>사용자별 채팅 호출 제한 초과</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -3466,14 +3468,14 @@
       <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>통과</t>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>guard 코드</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>설명</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -3486,12 +3488,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>INJECTION</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -3504,12 +3506,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NUMBER_UNVERIFIED</t>
+          <t>INJECTION</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
+          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
@@ -3522,12 +3524,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ADVICE</t>
+          <t>NUMBER_UNVERIFIED</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 투자 권유 표현</t>
+          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -3540,12 +3542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PROMPT_LEAK</t>
+          <t>ADVICE</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+          <t>출력 교체 — 투자 권유 표현</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
@@ -3555,91 +3557,71 @@
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PROMPT_LEAK</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>API ID</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/auth/signup</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>회원가입</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>FR-001</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3654,12 +3636,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/signup</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>회원가입</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3669,7 +3651,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>FR-002</t>
+          <t>FR-001</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -3677,7 +3659,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3692,34 +3674,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>가상계좌 개설</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Bearer</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>FR-003, FR-004</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
-        </is>
-      </c>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3729,7 +3707,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3739,7 +3717,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>내 계좌·잔액 조회</t>
+          <t>가상계좌 개설</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3749,15 +3727,19 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>FR-003, FR-004</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3767,17 +3749,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/primary</t>
+          <t>/api/v1/accounts</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 변경</t>
+          <t>내 계좌·잔액 조회</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3787,7 +3769,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>FR-004</t>
+          <t>FR-006</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -3795,7 +3777,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3805,17 +3787,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/charge</t>
+          <t>/api/v1/accounts/{accountId}/primary</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>충전</t>
+          <t>대표 계좌 변경</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3825,7 +3807,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>FR-005</t>
+          <t>FR-004</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -3833,7 +3815,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3848,12 +3830,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/aliases</t>
+          <t>/api/v1/accounts/{accountId}/charge</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>별칭 등록</t>
+          <t>충전</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3863,7 +3845,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>FR-007</t>
+          <t>FR-005</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -3871,7 +3853,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3881,7 +3863,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3891,7 +3873,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>별칭 목록</t>
+          <t>별칭 등록</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3901,7 +3883,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>FR-008</t>
+          <t>FR-007</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -3909,7 +3891,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3924,12 +3906,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfers?cursor&amp;size</t>
+          <t>/api/v1/aliases</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록</t>
+          <t>별칭 목록</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3939,19 +3921,15 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>FR-011</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
-        </is>
-      </c>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3961,17 +3939,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads</t>
+          <t>/api/v1/transfers?cursor&amp;size</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>새 대화</t>
+          <t>송금 내역 목록</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3981,15 +3959,19 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>FR-013</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+          <t>FR-011</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4004,12 +3986,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads/{threadId}/messages</t>
+          <t>/api/v1/chat/threads</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지</t>
+          <t>새 대화</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4019,19 +4001,15 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Spring이 I-01 호출. 호출 제한 적용</t>
-        </is>
-      </c>
+          <t>FR-013</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4046,12 +4024,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
+          <t>/api/v1/chat/threads/{threadId}/messages</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>송금 확정([보내기])</t>
+          <t>채팅 메시지</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4061,19 +4039,19 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>FR-010, NFR-001, NFR-009, NFR-010</t>
+          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>AI 경로를 거치지 않음</t>
+          <t>Spring이 I-01 호출. 호출 제한 적용</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4083,17 +4061,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/details/{detailId}</t>
+          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>송금 확정([보내기])</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4103,61 +4081,61 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FR-016, FR-019</t>
+          <t>FR-010, NFR-001, NFR-009, NFR-010</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Spring이 I-02 호출</t>
+          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>/internal/chat</t>
+          <t>/api/v1/chat/details/{detailId}</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>채팅 처리(LangGraph 구동)</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, NFR-005, NFR-006</t>
+          <t>FR-016, FR-019</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>Spring이 I-02 호출</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4167,17 +4145,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/internal/details/{detailId}</t>
+          <t>/internal/chat</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 생성</t>
+          <t>채팅 처리(LangGraph 구동)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4187,7 +4165,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FR-016, NFR-005, NFR-006</t>
+          <t>FR-014, FR-015, NFR-005, NFR-006</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4199,27 +4177,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>내부 FastAPI→Spring</t>
+          <t>내부 Spring→FastAPI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>/internal/transfer-requests</t>
+          <t>/internal/details/{detailId}</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 생성(확인 카드용)</t>
+          <t>상세 보고서 생성</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4229,88 +4207,132 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+          <t>FR-016, NFR-005, NFR-006</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 도구. 실행은 하지 않음</t>
+          <t>FastAPI 쪽 API</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>내부 FastAPI→Spring</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>/internal/transfer-requests</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청 생성(확인 카드용)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph 도구. 실행은 하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>내부 FastAPI→Spring</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>/internal/transfers?from&amp;to&amp;cursor&amp;size</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>송금 내역·합계 조회</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Bearer(사용자 JWT 전달)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>FR-012, NFR-002, NFR-005, NFR-006</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>LangGraph 도구. 합계는 Spring 계산</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A31:H48"/>
-  <mergeCells count="28">
+  <autoFilter ref="A32:H49"/>
+  <mergeCells count="30">
+    <mergeCell ref="C14:H14"/>
     <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C23:H23"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C22:H22"/>
     <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="B28:H28"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="B30:H30"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="B29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4322,7 +4344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4762,17 +4784,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>password</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4782,12 +4804,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>계좌 비밀번호(숫자 4자리, 해시로 저장)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>••••</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4826,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4819,12 +4841,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12자리 자동 발급</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4863,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4856,12 +4878,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>12자리 자동 발급</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4900,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.balance</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4893,12 +4915,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부(첫 계좌면 true)</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4910,59 +4932,59 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부(첫 계좌면 true)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4972,17 +4994,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4992,12 +5014,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5036,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].accountNumber</t>
+          <t>data.accounts[].accountId</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -5029,12 +5051,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5073,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].balance</t>
+          <t>data.accounts[].accountNumber</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -5066,12 +5088,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5110,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>data.accounts[].primary</t>
+          <t>data.accounts[].balance</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5103,12 +5125,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 여부</t>
+          <t>잔액(원)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
@@ -5120,59 +5142,59 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>data.accounts[].primary</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>대표 계좌 여부</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,12 +5209,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5202,12 +5224,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>대표로 바꿀 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5241,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5239,7 +5261,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>대표로 바꿀 계좌 ID</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5261,12 +5283,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>data.primary</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5276,12 +5298,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -5293,22 +5315,34 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>data.primary</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5323,14 +5357,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -5348,14 +5382,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -5363,39 +5397,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5410,12 +5432,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Path accountId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5425,12 +5447,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>충전할 계좌 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5469,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Path accountId</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5462,12 +5484,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>충전 금액(원)</t>
+          <t>충전할 계좌 ID</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5501,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>data.accountId</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5499,12 +5521,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>계좌 ID</t>
+          <t>충전 금액(원)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5543,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>data.balance</t>
+          <t>data.accountId</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -5536,12 +5558,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>충전 후 잔액(원)</t>
+          <t>계좌 ID</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5553,22 +5575,34 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>data.balance</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>충전 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5583,14 +5617,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5608,14 +5642,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>ACCOUNT_NOT_FOUND</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>계좌 없음</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -5633,54 +5667,42 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>INVALID_AMOUNT</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>충전 금액이 0 이하</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n"/>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INVALID_AMOUNT</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>충전 금액이 0 이하</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5695,7 +5717,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5710,12 +5732,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5754,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>accountNumber</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5747,12 +5769,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5764,17 +5786,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>data.aliasId</t>
+          <t>accountNumber</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5784,12 +5806,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>상대 계좌번호</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5806,12 +5828,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>data.alias</t>
+          <t>data.aliasId</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5821,12 +5843,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5865,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>data.accountNumber</t>
+          <t>data.alias</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5858,12 +5880,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5902,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>data.ownerName</t>
+          <t>data.accountNumber</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5895,12 +5917,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -5912,22 +5934,34 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
+          <t>data.ownerName</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5942,14 +5976,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -5957,39 +5991,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5999,17 +6021,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].aliasId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6019,12 +6041,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>별칭 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6063,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].alias</t>
+          <t>data.aliases[].aliasId</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6056,12 +6078,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>별칭</t>
+          <t>별칭 ID</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6100,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].accountNumber</t>
+          <t>data.aliases[].alias</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6093,12 +6115,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>계좌번호</t>
+          <t>별칭</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6137,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>data.aliases[].ownerName</t>
+          <t>data.aliases[].accountNumber</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6130,12 +6152,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>예금주 이름</t>
+          <t>계좌번호</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6147,59 +6169,59 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>data.aliases[].ownerName</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
+          <t>예금주 이름</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6214,27 +6236,27 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6251,12 +6273,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6266,12 +6288,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>묶음 크기(기본 20)</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -6283,32 +6305,32 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6347,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6340,12 +6362,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6384,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -6377,12 +6399,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6421,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -6414,12 +6436,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6458,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6451,12 +6473,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6495,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -6488,12 +6510,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6510,27 +6532,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2026-09-27T10:01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -6547,27 +6569,27 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -6579,59 +6601,59 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6641,12 +6663,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>data.threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -6661,12 +6683,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Spring이 발급, 사용자와 묶어 저장</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6678,59 +6700,59 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>data.threadId</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>Spring이 발급, 사용자와 묶어 저장</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>th_5b21...</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6745,7 +6767,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Path threadId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -6760,12 +6782,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>대화 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6804,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Path threadId</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6797,12 +6819,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>대화 ID</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -6814,12 +6836,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6834,12 +6856,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6878,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6871,12 +6893,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6915,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6903,17 +6925,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6952,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6945,12 +6967,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6989,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6982,12 +7004,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7026,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7019,12 +7041,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -7041,12 +7063,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7056,12 +7078,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -7078,12 +7100,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7093,12 +7115,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7115,12 +7137,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7130,12 +7152,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7174,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7167,12 +7189,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7211,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -7204,12 +7226,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7248,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7241,12 +7263,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
@@ -7258,22 +7280,34 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>data.detailId</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7288,14 +7322,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>THREAD_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>대화 없음(또는 남의 대화)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -7313,14 +7347,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>RATE_LIMITED</t>
+          <t>THREAD_NOT_FOUND</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>대화 없음(또는 남의 대화)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
@@ -7338,14 +7372,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>RATE_LIMITED</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>사용자별 채팅 호출 제한 초과</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -7353,39 +7387,27 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7400,7 +7422,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Path requestId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7415,12 +7437,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>확인 카드의 요청ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7432,17 +7454,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>data.transferId</t>
+          <t>Path requestId</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7452,12 +7474,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>확인 카드의 요청ID</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7491,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>password</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -7489,12 +7511,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>출금 계좌 비밀번호(숫자 4자리)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>••••</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7533,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.transferId</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -7526,12 +7548,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7570,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7563,12 +7585,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7607,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>data.balanceAfter</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -7600,12 +7622,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>송금 후 잔액(원)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -7617,22 +7639,34 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>data.fromAccountNumber</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
+          <t>출금 계좌</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>987654321098</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7642,22 +7676,34 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr"/>
+          <t>data.balanceAfter</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
+          <t>송금 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7672,14 +7718,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -7697,14 +7743,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>이미 확정된 송금 요청</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -7722,14 +7768,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -7747,14 +7793,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>이미 쓴 송금 요청(확정됨 또는 비밀번호 오류로 폐기)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
@@ -7762,113 +7808,77 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_OWNED</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>내 계좌가 아님</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_PASSWORD_INVALID</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>답변의 detailId</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>dt_91c2...</t>
-        </is>
-      </c>
+          <t>계좌 비밀번호 불일치 — 송금 요청ID도 폐기</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INSUFFICIENT_BALANCE</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>dt_91c2...</t>
-        </is>
-      </c>
+          <t>잔액 부족</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7878,12 +7888,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -7898,12 +7908,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문(클릭할 때 생성)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7915,32 +7925,32 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>답변의 detailId</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -7957,27 +7967,27 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -7994,7 +8004,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -8004,17 +8014,17 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>상세 보고서 본문(클릭할 때 생성)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8026,22 +8036,34 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
+          <t>data.table.columns</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>String[]</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
+          <t>표 머리글</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>["항목", ...]</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -8051,22 +8073,34 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>data.table.rows</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>String[][]</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+          <t>표 행</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>[[...]]</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8076,133 +8110,109 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>th_5b21...</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>엄마한테 1만원 보내줘</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8212,12 +8222,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -8232,12 +8242,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8259,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8269,12 +8279,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
@@ -8286,12 +8296,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -8301,17 +8311,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8338,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -8338,17 +8348,17 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8375,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -8375,17 +8385,17 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8412,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -8417,12 +8427,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -8439,12 +8449,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8454,12 +8464,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8486,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -8491,12 +8501,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -8513,12 +8523,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8528,12 +8538,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8560,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -8565,12 +8575,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8597,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -8602,12 +8612,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8634,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -8639,12 +8649,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
@@ -8656,37 +8666,49 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr"/>
-      <c r="E127" s="2" t="inlineStr"/>
+          <t>data.table.rows</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>String[][]</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
+          <t>표 행</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>[["영업이익","...","..."]]</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -8696,34 +8718,34 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -8733,12 +8755,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>상세 보기 ID(분석 답변일 때)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8750,39 +8772,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8792,32 +8802,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8829,32 +8839,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8881,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -8881,17 +8891,17 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>상세 보고서 본문</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8903,22 +8913,34 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="inlineStr"/>
+          <t>data.table.columns</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>String[]</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
+          <t>표 머리글</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>["항목", ...]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8928,37 +8950,49 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="2" t="inlineStr"/>
+          <t>data.table.rows</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>String[][]</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
+          <t>표 행</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>[[...]]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8968,93 +9002,69 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>재무제표 기준·미공시 표시</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>123456789012</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>엄마</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9069,12 +9079,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -9084,12 +9094,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9111,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -9116,17 +9126,17 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9148,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9153,17 +9163,17 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
@@ -9175,17 +9185,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9195,12 +9205,12 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9227,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.requestId</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -9232,12 +9242,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9264,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9269,12 +9279,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9301,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>data.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -9306,12 +9316,12 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9323,22 +9333,34 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
+          <t>data.fromAccountNumber</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
+          <t>출금 계좌(대표 계좌)</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>987654321098</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9348,22 +9370,34 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="inlineStr"/>
+          <t>data.amount</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9373,133 +9407,109 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
+          <t>data.expiresAt</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr"/>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ALIAS_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>등록되지 않은 별칭</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9514,25 +9524,29 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
+          <t>Bearer {JWT}</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Bearer eyJ...</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9547,27 +9561,27 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>Query from</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
+          <t>시작일(yyyy-MM-dd)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9579,17 +9593,17 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>Query to</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -9599,12 +9613,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>종료일(yyyy-MM-dd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9630,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -9631,19 +9645,15 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9653,12 +9663,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -9668,17 +9678,17 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>기본 20</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9705,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.sentTotal</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -9710,12 +9720,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
@@ -9732,12 +9742,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.receivedTotal</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -9747,12 +9757,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9779,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.count</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9784,12 +9794,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>기간 내 건수</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9816,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9821,12 +9831,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9853,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -9858,12 +9868,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>SENT / RECEIVED</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>SENT</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9890,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -9895,12 +9905,12 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -9917,27 +9927,27 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].counterpartAccountNumber</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>상대 계좌</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
@@ -9954,12 +9964,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -9969,12 +9979,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -9986,25 +9996,136 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].createdAt</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>시각(ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:01:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>data.nextCursor</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:G168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지: REST → 비동기 → gRPC 단계별 처리량·스레드 비교, 가짜 LLM</t>
+          <t>채팅 메시지: REST(RestClient) → 비동기(WebClient) 단계별 처리량·스레드 비교, 가짜 LLM</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>NFR-041</t>
+          <t>NFR-042</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3단계 gRPC</t>
+          <t>3단계 MCP</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Spring ↔ FastAPI 구간만. HTTP/2 동시 접속 대응(트래픽 추정 기준 동시 사용자 약 992명, 버퍼 약 4,960명), REST 대비 부하 테스트 수치</t>
+          <t>송금·계좌 도구(조회·요청 생성까지, 실행 권한 없음), DART 검색 도구</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2959,77 +2959,44 @@
       <c r="G69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>NFR-042</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>NFR-043</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>로드맵</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>4단계 MCP</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>송금·계좌 도구(조회·요청 생성까지, 실행 권한 없음), DART 검색 도구</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>NFR-043</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>테스트</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>계좌 동시성 정합성</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>동시 계좌 개설(같은/다른 Idempotency-Key), 동시 대표 계좌 변경 후 확인: 대표 계좌 항상 1개, 멱등키 재사용 시 신규 계좌 미생성. 실제 PostgreSQL(Testcontainers)로 검증(목·가짜 DB 사용 안 함)</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>E-03, E-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G71"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장</t>
+          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015)</t>
+          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015). 송금 발화 평가 세트(정상·누락·애매)로 금액·수취인 일치율, 되묻기 재현율, 틀린 확인 카드 수(목표 0) 측정. LLM 추출만 → 스키마 검증 → 원문 대조 순으로 하나씩 추가</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0</t>
+          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0. 락 없는 버전(기준선)·FOR UPDATE·@Version과 위반 건수·TPS 비교(측정 브랜치에서만)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>평가 세트로 수치 측정, 청킹·검색 방식 비교</t>
+          <t>평가 세트(질문–정답 청크)로 Recall@5·MRR 측정, 청킹·검색 방식 비교. 벡터 검색으로 시작하고, BM25(RRF)·재순위는 지표로 문제가 확인되면 비교 후 도입</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2995,8 +2995,41 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>NFR-044</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>질문 인식 측정</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>평가 세트로 의도 분류 정확도(재무·본문·송금·내역)와 기업명 인식률(삼전 같은 구어 표현 포함) 측정. 정식 기업명 일치로 시작하고, 별칭 사전·오타 허용은 인식률 문제가 확인되면 도입</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 제한 값 미정. 초과 시 HTTP 429 RATE_LIMITED</t>
+          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 체크포인터 + threadId. 대화방 목록 화면 없음</t>
+          <t>LangGraph 체크포인터 + threadId. 대화방 목록 화면 없음. MVP는 메모리 체크포인터(워커 1개, 재시작 시 기록 소실) — 문제가 확인되면 PostgreSQL 체크포인터로 전환. 기록에는 가린 문장만 남기고 인젝션으로 막힌 문장은 남기지 않음</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>초기: 재무정보 일괄다운로드(TXT) 최근 2년을 수동으로 받아 적재 스크립트로 1회. 이후: 하루 1회 다중회사 주요계정 API(fnlttMultiAcnt, 최대 100개 → 코스피200은 2번 호출). 비교 지표 계정만 저장</t>
+          <t>하루 1회 다중회사 주요계정 API(fnlttMultiAcnt, 최대 100개 → 코스피200은 2번 호출)로 최근 2년(올해·작년) 4개 보고서를 받아 적재. 초기 적재도 같은 호출(TXT 일괄 다운로드 대신). 비교 지표 계정(매출액·영업이익·당기순이익)만, 연결·별도 모두 저장</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$31:$H$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>하루 1회 공시서류원본파일 API(document.xml) → 사업의 내용 추출 → 청킹 → 임베딩 → pgvector. 회사별 최신 보고서만 유지</t>
+          <t>하루 1회 공시검색 API(list.json)로 회사별 최신 정기보고서를 찾고(접수번호가 같으면 건너뜀) → 공시서류원본파일 API(document.xml) → 사업의 내용 추출 → 청킹 → 임베딩 → pgvector. 회사별 최신 보고서만 유지</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4303,36 +4303,36 @@
   </sheetData>
   <autoFilter ref="A32:H49"/>
   <mergeCells count="30">
-    <mergeCell ref="C14:H14"/>
     <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C22:H22"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B30:H30"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C21:H21"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:H19"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="B29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10153,6 +10153,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -10621,6 +10622,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>JWT 발급. 화면은 localStorage에 두고 Authorization: Bearer로 보냄</t>
+          <t>JWT 발급. 화면은 localStorage에 두고 Authorization: Bearer로 보냄. 로그아웃은 화면이 토큰과 대화 기록을 지우고 로그인으로 이동(서버 무효화 없음, 만료 1시간)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 체크포인터 + threadId. 대화방 목록 화면 없음. MVP는 메모리 체크포인터(워커 1개, 재시작 시 기록 소실) — 문제가 확인되면 PostgreSQL 체크포인터로 전환. 기록에는 가린 문장만 남기고 인젝션으로 막힌 문장은 남기지 않음</t>
+          <t>LangGraph 체크포인터 + threadId. 대화방 목록 화면 없음. MVP는 메모리 체크포인터(워커 1개, 재시작 시 기록 소실) — 문제가 확인되면 PostgreSQL 체크포인터로 전환. 기록에는 가린 문장만 남기고 인젝션으로 막힌 문장은 남기지 않음. 화면은 threadId·말풍선을 탭의 sessionStorage에 두어 메뉴를 옮겨도 같은 대화를 잇고 [새 대화]로 새로 시작. 탭을 닫거나 로그아웃·로그인하면 비움</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리, UI 디자인. 남김: 계좌 소유자 확인, 비밀번호 해시</t>
+          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리. 화면 스타일은 현대닷컴 톤 공통 CSS 하나만(화면별 디자인 없음). 남김: 계좌 소유자 확인, 비밀번호 해시</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>직접 만든 경쟁사 목록(MVP는 주요 업종 일부, 업종 미정) + 사용자 지정 우선. 최대 3개. 같은 분기 공시가 없으면 비교에서 빼고 '미공시' 표시. 채팅은 요약 + 표, 상세 보기는 전체, 차트 없음</t>
+          <t>직접 만든 경쟁사 목록(MVP 업종: 반도체·자동차·2차전지·인터넷) + 사용자 지정 우선. 질문에 '경쟁'이 있고 기업을 하나만 말하면 그 업종의 경쟁사를 더함. 최대 3개(질문한 기업 포함). 같은 분기 공시가 없으면 비교에서 빼고 '미공시' 표시. 채팅은 요약 + 표, 상세 보기는 전체, 차트 없음</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -10597,13 +10597,19 @@
           <t>한계 TPS (스트레스 측정값)</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
+      <c r="B28" s="20" t="n">
+        <v>19</v>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>스트레스 테스트로 잰 서버 1대의 한계 TPS를 입력</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>스트레스 측정(2026-10-20, 앱 2 vCPU·2GiB, 가짜 LLM): 재무·송금 채팅 p95 &lt; 5,196ms 등 부하 테스트 기준을 지킨 마지막 단계. 개요 6절 '성능 측정' 참고</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>스트레스 측정(2026-10-20, 앱 2 vCPU·2GiB, 가짜 LLM): 재무·송금 채팅 p95 &lt; 5,196ms 등 부하 테스트 기준을 지킨 마지막 단계. 개요 6절 '성능 측정' 참고</t>
+          <t>스트레스 측정(2026-10-20, 앱 2 vCPU·2GiB, 가짜 LLM, 채팅 질문이 실패해도 세션을 이어가는 시나리오): 재무·송금 채팅 p95 &lt; 5,196ms 등 부하 테스트 기준을 지킨 마지막 단계(180초 유지로 확인). 개요 6절 '성능 측정' 참고</t>
         </is>
       </c>
     </row>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -10597,13 +10597,19 @@
           <t>한계 TPS (스트레스 측정값)</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
+      <c r="B28" s="20" t="n">
+        <v>15</v>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>스트레스 테스트로 잰 서버 1대의 한계 TPS를 입력</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>스트레스 측정(2026-10-20, 앱 2 vCPU·2GiB, 가짜 LLM, 채팅 질문이 실패해도 세션을 이어가는 시나리오): 재무·송금 채팅 p95 &lt; 5,196ms 등 부하 테스트 기준을 지킨 마지막 단계(180초 유지로 확인). 개요 6절 '성능 측정' 참고</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,7 +13,7 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$168</definedName>
   </definedNames>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1466,15 +1466,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>내역</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>입금 알림</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
+          <t>송금 완료 알림</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>송금 확정 후 보낸 사람(출금)·받은 사람(입금) 모두에게 알림. 확정 트랜잭션에 알림 행을 함께 쓰고(outbox) 발송은 비동기라 확정 응답을 늦추지 않음. 접속 중이면 SSE로 바로, 아니면 알림 목록에 남김. (송금 ID, 받는 사람) 유일 키로 한 번만 표시</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>추후</t>
@@ -1570,83 +1574,75 @@
       <c r="G28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>NFR-001</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>구조</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>AI 경로에 송금 실행 권한 없음</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph는 조회·송금 요청 생성까지. 실행은 사용자가 [보내기]를 누르면 Spring이 함</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>E-12, I-03</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>FR-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>내역</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>송금 내역 추이 그래프</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>기간(일·월, 1개월~전체)별 보낸·받은 금액 추이. 집계는 Spring이 SQL로 계산(LLM 아님). 내역 100만 건 계정에서도 동작(NFR-046)</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>NFR-002</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>구조</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>LLM은 숫자를 만들지 않음</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>돈 숫자는 Spring, DART 재무 숫자는 FastAPI 계산 코드. LLM은 받은 숫자를 설명만</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>FR-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>송금</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>예약(정기) 송금</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>채팅·MCP로 규칙 초안(예: 매월 25일 엄마에게 10만 원) → 확인 카드에서 계좌 비밀번호로 등록. 실행은 스케줄러가 규칙대로(LLM 없음), (규칙 ID, 실행일) 유일 키로 한 번만. 상태: 예정 → 처리 중 → 완료·실패·확인 필요, 결과는 알림(FR-024)</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NFR-003</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1661,12 +1657,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>장애 격리</t>
+          <t>AI 경로에 송금 실행 권한 없음</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연에도 송금·계좌는 정상. 채팅만 AI_SERVER_UNAVAILABLE</t>
+          <t>LangGraph는 조회·송금 요청 생성까지. 실행은 사용자가 [보내기]를 누르면 Spring이 함</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1676,14 +1672,14 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-12, I-03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NFR-004</t>
+          <t>NFR-002</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1698,12 +1694,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1단계 내부 REST</t>
+          <t>LLM은 숫자를 만들지 않음</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Spring ↔ FastAPI 내부 REST, Spring은 RestClient(기준 수치)</t>
+          <t>돈 숫자는 Spring, DART 재무 숫자는 FastAPI 계산 코드. LLM은 받은 숫자를 설명만</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1711,12 +1707,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-003</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 내부 전용</t>
+          <t>장애 격리</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>/internal/** 는 Docker 내부망에서만 호출. 브라우저는 Spring만 호출</t>
+          <t>FastAPI 장애·지연에도 송금·계좌는 정상. 채팅만 AI_SERVER_UNAVAILABLE</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1746,14 +1746,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>I-01, I-02, I-03, I-04</t>
+          <t>E-11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>NFR-004</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>내부 호출 시 JWT 전달</t>
+          <t>1단계 내부 REST</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Spring → FastAPI → Spring으로 사용자 JWT를 그대로 전달하고 Spring이 본인 확인. AI가 다른 사용자 계좌에 접근 불가</t>
+          <t>Spring ↔ FastAPI 내부 REST, Spring은 RestClient(기준 수치)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1781,16 +1781,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>I-01, I-02, I-03, I-04</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NFR-007</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1805,12 +1801,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>인증 방식</t>
+          <t>FastAPI 내부 전용</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>JWT는 localStorage + Bearer 헤더. JSP 페이지는 인증 없이 렌더링하고 데이터는 fetch. 쿠키 미사용이라 CSRF 해당 없음</t>
+          <t>/internal/** 는 Docker 내부망에서만 호출. 브라우저는 Spring만 호출</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1818,12 +1814,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>I-01, I-02, I-03, I-04</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NFR-008</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>금액 타입</t>
+          <t>내부 호출 시 JWT 전달</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>원 단위 정수(Long)</t>
+          <t>Spring → FastAPI → Spring으로 사용자 JWT를 그대로 전달하고 Spring이 본인 확인. AI가 다른 사용자 계좌에 접근 불가</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1851,12 +1851,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>I-01, I-02, I-03, I-04</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NFR-009</t>
+          <t>NFR-007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1866,17 +1870,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>송금</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>동시 송금 잔액 정합성</t>
+          <t>인증 방식</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>동시에 송금해도 잔액이 음수가 되거나 어긋나지 않음</t>
+          <t>JWT는 localStorage + Bearer 헤더. JSP 페이지는 인증 없이 렌더링하고 데이터는 fetch. 쿠키 미사용이라 CSRF 해당 없음</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1884,16 +1888,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>E-12</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NFR-010</t>
+          <t>NFR-008</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>송금</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>중복 클릭 1회 송금</t>
+          <t>금액 타입</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>요청ID 1회용 — [보내기]를 여러 번 눌러도 송금은 한 번</t>
+          <t>원 단위 정수(Long)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1921,16 +1921,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>E-12</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NFR-011</t>
+          <t>NFR-009</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1940,17 +1936,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>범위 원칙</t>
+          <t>동시 송금 잔액 정합성</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리. 화면 스타일은 현대닷컴 톤 공통 CSS 하나만(화면별 디자인 없음). 남김: 계좌 소유자 확인, 비밀번호 해시</t>
+          <t>동시에 송금해도 잔액이 음수가 되거나 어긋나지 않음</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1958,12 +1954,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NFR-012</t>
+          <t>NFR-010</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>가드레일</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>입력: 인젝션 규칙</t>
+          <t>중복 클릭 1회 송금</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
+          <t>요청ID 1회용 — [보내기]를 여러 번 눌러도 송금은 한 번</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1991,12 +1991,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>NFR-013</t>
+          <t>NFR-011</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2006,17 +2010,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>가드레일</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>입력: 개인정보 가림</t>
+          <t>범위 원칙</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>주민·카드번호를 가린 뒤 진행(차단 아님)</t>
+          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리. 화면 스타일은 현대닷컴 톤 공통 CSS 하나만(화면별 디자인 없음). 남김: 계좌 소유자 확인, 비밀번호 해시</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2029,7 +2033,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>NFR-014</t>
+          <t>NFR-012</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2044,12 +2048,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>구조화: 송금 값 검증</t>
+          <t>입력: 인젝션 규칙</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015). 송금 발화 평가 세트(정상·누락·애매)로 금액·수취인 일치율, 되묻기 재현율, 틀린 확인 카드 수(목표 0) 측정. LLM 추출만 → 스키마 검증 → 원문 대조 순으로 하나씩 추가</t>
+          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2062,7 +2066,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NFR-015</t>
+          <t>NFR-013</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>검색: 공시 본문 구분</t>
+          <t>입력: 개인정보 가림</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>공시 본문을 '데이터' 구분자로 감싸서 LLM에 전달</t>
+          <t>주민·카드번호를 가린 뒤 진행(차단 아님)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2095,7 +2099,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>NFR-016</t>
+          <t>NFR-014</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2110,12 +2114,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>출력: 숫자 환각 가드 1~3단계</t>
+          <t>구조화: 송금 값 검증</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>① 프롬프트만(기준선) → ② 숫자 존재 대조 → ③ 항목·값 쌍 대조. 단계마다 평가 세트로 측정(정답은 재무 테이블, 자동 채점). 근거 범위: 재무 지표 4개는 항목·값 쌍 대조, 사업의 내용 본문 숫자는 검색 조각과 존재 대조 + 출처 표시. 걸리면 guard=NUMBER_UNVERIFIED</t>
+          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015). 송금 발화 평가 세트(정상·누락·애매)로 금액·수취인 일치율, 되묻기 재현율, 틀린 확인 카드 수(목표 0) 측정. LLM 추출만 → 스키마 검증 → 원문 대조 순으로 하나씩 추가</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2128,7 +2132,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NFR-017</t>
+          <t>NFR-015</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2143,12 +2147,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>출력: 투자 권유 표현</t>
+          <t>검색: 공시 본문 구분</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>표현 목록으로 판정 → guard=ADVICE</t>
+          <t>공시 본문을 '데이터' 구분자로 감싸서 LLM에 전달</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2161,7 +2165,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NFR-018</t>
+          <t>NFR-016</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2176,12 +2180,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>출력: 시스템 프롬프트 유출 감지</t>
+          <t>출력: 숫자 환각 가드 1~3단계</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK</t>
+          <t>① 프롬프트만(기준선) → ② 숫자 존재 대조 → ③ 항목·값 쌍 대조. 단계마다 평가 세트로 측정(정답은 재무 테이블, 자동 채점). 근거 범위: 재무 지표 4개는 항목·값 쌍 대조, 사업의 내용 본문 숫자는 검색 조각과 존재 대조 + 출처 표시. 걸리면 guard=NUMBER_UNVERIFIED</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2194,110 +2198,110 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>NFR-017</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>출력: 투자 권유 표현</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>표현 목록으로 판정 → guard=ADVICE</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>NFR-018</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>출력: 시스템 프롬프트 유출 감지</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>NFR-019</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>가드레일</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>공통: 차단 처리</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>걸리면 정상 응답(success=true) + 고정 문장 + 판정 코드. 가드별 행동 표. 가드는 LangGraph 노드, 걸리면 조건부 엣지로 END</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>E-11</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>NFR-020</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>가드레일</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>입력: 분류 모델</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Prompt Guard 추가 후 규칙만 쓸 때와 전후 측정(한국어 성능 확인)</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>NFR-021</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>가드레일</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>출력: 숫자 가드 4단계</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>표기 정규화(조·억·%·반올림) → 오탐 감소 측정</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NFR-022</t>
+          <t>NFR-020</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2312,12 +2316,12 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>출력: 숫자 가드 5단계</t>
+          <t>입력: 분류 모델</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>자리표시자 구조(숫자는 코드가 채움) → 환각 구조적 0</t>
+          <t>Prompt Guard 추가 후 규칙만 쓸 때와 전후 측정(한국어 성능 확인)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2330,7 +2334,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NFR-023</t>
+          <t>NFR-021</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2345,12 +2349,12 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>검색: 공시 본문 검사</t>
+          <t>출력: 숫자 가드 4단계</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>간접 인젝션 검사</t>
+          <t>표기 정규화(조·억·%·반올림) → 오탐 감소 측정</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2361,46 +2365,42 @@
       <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>NFR-024</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>NFR-022</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>채팅 호출 횟수 제한</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>E-11</t>
-        </is>
-      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>출력: 숫자 가드 5단계</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>자리표시자 구조(숫자는 코드가 채움) → 환각 구조적 0</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>NFR-025</t>
+          <t>NFR-023</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>가드레일</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>호출 제한 Redis 이전</t>
+          <t>검색: 공시 본문 검사</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>서버를 2대 이상으로 늘리면 카운터 공유를 위해 Redis로 이전</t>
+          <t>간접 인젝션 검사</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>NFR-026</t>
+          <t>NFR-024</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2443,17 +2443,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>관측</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>자체 로그</t>
+          <t>채팅 호출 횟수 제한</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>판정 코드, 노드별 소요 시간을 로그 테이블에 기록</t>
+          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2461,12 +2461,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>NFR-027</t>
+          <t>NFR-025</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2476,17 +2480,17 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>관측</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>LLM 추적</t>
+          <t>호출 제한 Redis 이전</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Langfuse</t>
+          <t>서버를 2대 이상으로 늘리면 카운터 공유를 위해 Redis로 이전</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2499,7 +2503,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NFR-028</t>
+          <t>NFR-026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2509,17 +2513,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>테스트</t>
+          <t>관측</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>트래픽 추정</t>
+          <t>자체 로그</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>TAM → SAM → SOM → MAU → DAU → 피크 → TPS. '트래픽 추정' 시트(수식). 피크는 개장 직후 30분 DAU의 17.2%(한국거래소 대용치), 버퍼 5배. 목표 약 93 TPS, 동시 사용자 약 992명(버퍼 약 4,960명)</t>
+          <t>판정 코드, 노드별 소요 시간을 로그 테이블에 기록</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2530,42 +2534,42 @@
       <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>NFR-029</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>NFR-027</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>LLM 지연 실측</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>실제 OpenAI로 지연을 재서 p50·p95·분포 기록. 가짜 LLM은 이 실측 분포를 그대로 재현(시드 고정)</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>관측</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>LLM 추적</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Langfuse</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>NFR-030</t>
+          <t>NFR-028</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2580,12 +2584,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>성능 테스트(API 단위)</t>
+          <t>트래픽 추정</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록: 전체 조회 → 오프셋 → 커서. p95 &lt; 500ms</t>
+          <t>TAM → SAM → SOM → MAU → DAU → 피크 → TPS. '트래픽 추정' 시트(수식). 피크는 개장 직후 30분 DAU의 17.2%(한국거래소 대용치), 버퍼 5배. 목표 약 93 TPS, 동시 사용자 약 992명(버퍼 약 4,960명)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2598,7 +2602,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>NFR-031</t>
+          <t>NFR-029</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2613,12 +2617,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>부하 테스트(전체 시나리오)</t>
+          <t>LLM 지연 실측</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>행동 유형 4개(DART 50%·송금 30%·내역 15%·가입 5%) 비율로 목표 TPS 유지, 가짜 LLM. 합격: 일반 API p95 &lt; 500ms, 채팅 p95 &lt; 가짜 지연 p95 + 1초, 에러율 &lt; 1%</t>
+          <t>실제 OpenAI로 지연을 재서 p50·p95·분포 기록. 가짜 LLM은 이 실측 분포를 그대로 재현(시드 고정)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2631,7 +2635,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NFR-032</t>
+          <t>NFR-030</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2646,12 +2650,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>스트레스 테스트</t>
+          <t>성능 테스트(API 단위)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>약 4,960 VU부터 무너질 때까지 늘려 한계점 기록(최소 DAU 전원 동시 34,608명까지 확인), 가짜 LLM. 한계 TPS로 버틸 수 있는 최대 피크 집중도 역산</t>
+          <t>송금 내역 목록: 전체 조회 → 오프셋 → 커서. p95 &lt; 500ms</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2664,7 +2668,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>NFR-033</t>
+          <t>NFR-031</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2679,12 +2683,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>로드맵 비교(API 단위)</t>
+          <t>부하 테스트(전체 시나리오)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지: REST(RestClient) → 비동기(WebClient) 단계별 처리량·스레드 비교, 가짜 LLM</t>
+          <t>행동 유형 4개(DART 50%·송금 30%·내역 15%·가입 5%) 비율로 목표 TPS 유지, 가짜 LLM. 합격: 일반 API p95 &lt; 500ms, 채팅 p95 &lt; 가짜 지연 p95 + 1초, 에러율 &lt; 1%</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2697,7 +2701,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>NFR-034</t>
+          <t>NFR-032</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>정합성 테스트(API 단위)</t>
+          <t>스트레스 테스트</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0. 락 없는 버전(기준선)·FOR UPDATE·@Version과 위반 건수·TPS 비교(측정 브랜치에서만)</t>
+          <t>약 4,960 VU부터 무너질 때까지 늘려 한계점 기록(최소 DAU 전원 동시 34,608명까지 확인), 가짜 LLM. 한계 TPS로 버틸 수 있는 최대 피크 집중도 역산</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2730,7 +2734,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>NFR-035</t>
+          <t>NFR-033</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2745,12 +2749,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>실제 OpenAI 검증</t>
+          <t>로드맵 비교(API 단위)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>전체 시나리오를 목표 TPS의 10%로 5분. 판정 없이 기록. OpenAI 429는 우리 에러와 분리 집계, 재시도 없음, 실행 전 예상 비용 기록</t>
+          <t>채팅 메시지: REST(RestClient) → 비동기(WebClient) 단계별 처리량·스레드 비교, 가짜 LLM</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2763,7 +2767,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NFR-036</t>
+          <t>NFR-034</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2778,12 +2782,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>정합성 테스트(API 단위)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Prometheus: Spring·FastAPI(HTTP 지연, Tomcat 스레드, DB 커넥션 풀, LLM 호출 시간, OpenAI 에러 수, 가드 판정 횟수), PostgreSQL(커넥션, 락 대기), cAdvisor(컨테이너 CPU·메모리), k6 remote write → Grafana 한 화면</t>
+          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0. 락 없는 버전(기준선)·FOR UPDATE·@Version과 위반 건수·TPS 비교(측정 브랜치에서만)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2796,7 +2800,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>NFR-037</t>
+          <t>NFR-035</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2811,12 +2815,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>측정 환경</t>
+          <t>실제 OpenAI 검증</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>앱(Spring·FastAPI·PostgreSQL)만 AWS t3.small 사양으로 제한, k6·Prometheus·Grafana는 제한 밖</t>
+          <t>전체 시나리오를 목표 TPS의 10%로 5분. 판정 없이 기록. OpenAI 429는 우리 에러와 분리 집계, 재시도 없음, 실행 전 예상 비용 기록</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2827,42 +2831,42 @@
       <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>NFR-038</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>NFR-036</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>테스트</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>스파이크·내구 테스트</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>장 마감 직후 급증, 장시간 유지</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>모니터링</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus: Spring·FastAPI(HTTP 지연, Tomcat 스레드, DB 커넥션 풀, LLM 호출 시간, OpenAI 에러 수, 가드 판정 횟수), PostgreSQL(커넥션, 락 대기), cAdvisor(컨테이너 CPU·메모리), k6 remote write → Grafana 한 화면</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>NFR-039</t>
+          <t>NFR-037</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2872,17 +2876,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>품질</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>RAG 검색 품질 측정</t>
+          <t>측정 환경</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>평가 세트(질문–정답 청크)로 Recall@5·MRR 측정, 청킹·검색 방식 비교. 벡터 검색으로 시작하고, BM25(RRF)·재순위는 지표로 문제가 확인되면 비교 후 도입</t>
+          <t>앱(Spring·FastAPI·PostgreSQL)만 AWS t3.small 사양으로 제한, k6·Prometheus·Grafana는 제한 밖</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2895,141 +2899,438 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>NFR-038</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>스파이크·내구 테스트</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>장 마감 직후 급증, 장시간 유지</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>NFR-039</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>RAG 검색 품질 측정</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>평가 세트(질문–정답 청크)로 Recall@5·MRR 측정, 청킹·검색 방식 비교. 벡터 검색으로 시작하고, BM25(RRF)·재순위는 지표로 문제가 확인되면 비교 후 도입</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t>NFR-040</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>로드맵</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>2단계 비동기 전환</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>WebClient. Java 17이라 가상 스레드 불가 → LLM 대기 중 스레드 반납, 동시 처리량 비교</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>추후</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>NFR-042</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>로드맵</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>3단계 MCP</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>송금·계좌 도구(조회·요청 생성까지, 실행 권한 없음), DART 검색 도구</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>송금·계좌 도구(조회·요청 생성·예약 송금 초안까지, 실행 권한 없음), DART 검색 도구. 에이전트 호출은 입장 제어(NFR-049)로 보호</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>추후</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>NFR-043</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>테스트</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>계좌 동시성 정합성</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>동시 계좌 개설(같은/다른 Idempotency-Key), 동시 대표 계좌 변경 후 확인: 대표 계좌 항상 1개, 멱등키 재사용 시 신규 계좌 미생성. 실제 PostgreSQL(Testcontainers)로 검증(목·가짜 DB 사용 안 함)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>E-03, E-05</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>NFR-044</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>품질</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>질문 인식 측정</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>평가 세트로 의도 분류 정확도(재무·본문·송금·내역)와 기업명 인식률(삼전 같은 구어 표현 포함) 측정. 정식 기업명 일치로 시작하고, 별칭 사전·오타 허용은 인식률 문제가 확인되면 도입</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>NFR-045</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>알림 대량 전달</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>송금 확정 → 알림 도착 p95 &lt; 1초(접속 중 사용자). 동시 접속 1천 → 1만으로 늘려 노드 하나의 한계(연결 수·초당 전달 수)를 재고 100만 명은 노드 수로 역산. 외부 푸시(FCM 기본 한도 분당 60만 건)는 1초 목표에서 제외. 알림 발송이 확정 p95를 늘리지 않는지 함께 확인</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NFR-046</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>내역 집계 조회 성능</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>내역 100만 건 계정에서 추이 조회 p95 &lt; 500ms(기간 1개월·1년·전체). (계좌, 시각) 복합 인덱스 집계 → 일별 요약 테이블 순으로 하나씩 바꿔 측정(NFR-030과 같은 시드·도구). 파티셔닝은 테이블 전체가 수억 행일 때만, 샤딩은 하지 않음(송금 하나가 두 샤드에 걸치면 한 트랜잭션으로 못 묶음)</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NFR-047</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>AI 시나리오 테스트</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>LLM이 사용자 역할(처음 쓰는 사람·급한 사람·오타·말 바꾸기)로 채팅 시나리오를 만들어 실제 API로 끝까지 진행. 합격은 규칙으로: 틀린 확인 카드 0, 턴 응답이 읽기 제한 안, 같은 되묻기 2회 이하, 내부 오류 문구 노출 0. LLM 판정은 이상 후보 표시만(사람이 확인). 실행 전 예상 비용 기록, 같은 세트 3회</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NFR-048</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>외부 연동 장애·배치 지연 대응</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>외부 API(DART·OpenAI·외부 이체망) 오류를 일시·한도·점검·영구로 나눠 처리: 일시 오류만 재시도(지수 백오프 + 지터), 응답 없는 쓰기는 재전송 대신 조회로 확인, 연속 실패는 차단기로 멈춤. 예약 송금이 한 시각에 몰리면 실행 시각 분산·워커 분할(SKIP LOCKED)·진행 상태 표시, 하루 마감 대사(NFR-034 SQL 3개). 외부 이체망은 가짜 서버로 장애 주입</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NFR-049</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>수평 확장·급증 대응</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>1대 한계(15 TPS, 피크 30분 약 4,800명)를 넘으면 순서대로: ① 입장 제어(사용자·API 키별 한도, 동시 처리 상한, 넘치면 429 + Retry-After, 송금 확정 우선, 쓰기 도구 멱등 키) ② 무상태화(대화 상태 PostgreSQL, 호출 제한·캐시 Redis) ③ nginx 뒤 FastAPI·Spring 여러 대(FastAPI부터), DB 커넥션 풀러 ④ LLM 토큰 예산. 1 → 2 → 4대에서 같은 stress.sh로 한계 TPS 비교</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>NFR-050</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>홈서버 망 분리·접근 통제</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Docker 네트워크를 앞단(터널 커넥터 ↔ Spring)·내부(Spring·FastAPI·DB)·외부 호출(터널 커넥터·FastAPI·collector만 인터넷으로)로 분리 — Spring·DB는 인터넷으로 못 나감. 들어오는 포트 0(터널로 웹 공개), 관리(SSH·Grafana·DB)와 배포는 VPN(사람·기기 단위 허용)으로만. 호스트 방화벽 기본 차단, Docker 포트는 127.0.0.1에만. 앱별 DB 계정(최소 권한)</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>NFR-051</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>홈서버 운영 점검</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>공개 전·분기마다: 네트워크(공인 IP·CGNAT·DDNS·업로드 대역폭·ISP 약관), 미들웨어(타임아웃 사슬, 로그 크기 제한, 재시작 정책·헬스체크), OS(보안 업데이트, 시간 동기, 디스크·메모리 경고, SSH 키 전용), DB(매일 백업 + 다른 곳 보관 + 복구 리허설, 커넥션 합 ≤ max_connections, 슬로우 쿼리 로그)</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G71"/>
+  <autoFilter ref="A1:G80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,7 +13,7 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$168</definedName>
   </definedNames>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3329,8 +3329,45 @@
       </c>
       <c r="G80" s="3" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>NFR-052</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>사업의 내용 재검색(LangGraph 루프)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>사업의 내용 답변에 근거 없는 숫자가 있으면(NUMBER_UNVERIFIED 조건) 질문을 검색어로 고쳐 써서 한 번 더 검색·답변. 최대 1회, 판정은 코드. 고친 검색어는 검색에만 쓴다. 지연(재검색 턴은 10초 읽기 제한 초과 예상)은 우선 그대로 두고 재검색 비율·재검색 후 통과율·턴 지연을 잰 뒤 개선</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G80"/>
+  <autoFilter ref="A1:G81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,9 +13,9 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1454,37 +1454,41 @@
       <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>FR-024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>송금 완료 알림</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>송금 확정 후 보낸 사람(출금)·받은 사람(입금) 모두에게 알림. 확정 트랜잭션에 알림 행을 함께 쓰고(outbox) 발송은 비동기라 확정 응답을 늦추지 않음. 접속 중이면 SSE로 바로, 아니면 알림 목록에 남김. (송금 ID, 받는 사람) 유일 키로 한 번만 표시</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>송금 확정 시 보낸 사람(출금)·받은 사람(입금)에게 알림. 알림 행은 확정 트랜잭션에 함께 저장((송금 ID, 받는 사람) 유일 키 — 커밋되면 반드시 남음), 커밋 뒤 접속 중인 사람에게 SSE로 보냄(확정 응답은 기다리지 않음). 놓친 알림은 목록으로. 화면은 Authorization 헤더를 붙이려고 EventSource 대신 fetch 스트림으로 받음(토큰을 URL에 넣지 않음). 서버 1대 기준이고 대량 전달은 NFR-045</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>E-12, E-14, E-15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3253,7 +3257,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1대 한계(15 TPS, 피크 30분 약 4,800명)를 넘으면 순서대로: ① 입장 제어(사용자·API 키별 한도, 동시 처리 상한, 넘치면 429 + Retry-After, 송금 확정 우선, 쓰기 도구 멱등 키) ② 무상태화(대화 상태 PostgreSQL, 호출 제한·캐시 Redis) ③ nginx 뒤 FastAPI·Spring 여러 대(FastAPI부터), DB 커넥션 풀러 ④ LLM 토큰 예산. 1 → 2 → 4대에서 같은 stress.sh로 한계 TPS 비교</t>
+          <t>1대 한계(15 TPS, 피크 30분 약 4,800명)를 넘으면 순서대로: ① 입장 제어(사용자·API 키별 한도, 동시 처리 상한, 넘치면 429 + Retry-After, 송금 확정 우선, 쓰기 도구 멱등 키) ② 무상태화(대화 상태 PostgreSQL, 호출 제한·캐시 Redis, 알림 SSE는 연결이 다른 서버에 있어도 닿게 Redis pub/sub) ③ nginx(NFR-053) 뒤 FastAPI·Spring 여러 대(FastAPI부터), DB 커넥션 풀러 ④ LLM 토큰 예산. 1 → 2 → 4대에서 같은 stress.sh로 한계 TPS 비교</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3286,7 +3290,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Docker 네트워크를 앞단(터널 커넥터 ↔ Spring)·내부(Spring·FastAPI·DB)·외부 호출(터널 커넥터·FastAPI·collector만 인터넷으로)로 분리 — Spring·DB는 인터넷으로 못 나감. 들어오는 포트 0(터널로 웹 공개), 관리(SSH·Grafana·DB)와 배포는 VPN(사람·기기 단위 허용)으로만. 호스트 방화벽 기본 차단, Docker 포트는 127.0.0.1에만. 앱별 DB 계정(최소 권한)</t>
+          <t>Docker 네트워크를 앞단(터널 커넥터 ↔ nginx ↔ Spring)·내부(Spring·FastAPI·DB)·외부 호출(터널 커넥터·FastAPI·collector만 인터넷으로)로 분리 — Spring·DB는 인터넷으로 못 나감. 들어오는 포트 0(터널로 웹 공개 — NFR-053의 80·443 포트포워딩을 대체), 관리(SSH·Grafana·DB)와 배포는 VPN(사람·기기 단위 허용)으로만. 호스트 방화벽 기본 차단, Docker 포트는 127.0.0.1에만. 앱별 DB 계정(최소 권한)</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3366,8 +3370,45 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>NFR-053</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>리버스 프록시·HTTPS(nginx)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>도메인을 붙이고 nginx를 유일한 입구로: TLS 종료(Let's Encrypt, 자동 갱신), 80은 443으로 넘김, Spring으로 프록시(X-Forwarded-For·Proto 전달). 공유기는 80·443만 nginx로 넘기고 Spring 8080은 공개 중단(127.0.0.1에만). 타임아웃은 nginx &gt; Spring 읽기 제한(채팅 10초·상세 30초), 알림 스트림(E-15)은 버퍼링 끄고 하트비트 간격보다 길게. 로그인·가입은 IP별 요청 제한(limit_req). 부하 측정 환경은 지금처럼 Spring 직접(기준선 유지)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>E-01, E-02, E-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G81"/>
+  <autoFilter ref="A1:G82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3378,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4419,12 +4460,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FR-010, NFR-001, NFR-009, NFR-010</t>
+          <t>FR-010, FR-024, NFR-001, NFR-009, NFR-010</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음</t>
+          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음. 확정 트랜잭션에 알림 행 저장(FR-024)</t>
         </is>
       </c>
     </row>
@@ -4473,54 +4514,54 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/internal/chat</t>
+          <t>/api/v1/notifications?cursor&amp;size</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>채팅 처리(LangGraph 구동)</t>
+          <t>알림 목록</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, NFR-005, NFR-006</t>
+          <t>FR-024</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>최신순 커서(E-09와 같은 규칙). 스트림이 끊긴 사이 놓친 알림을 채움</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4530,39 +4571,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>/internal/details/{detailId}</t>
+          <t>/api/v1/notifications/stream</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 생성</t>
+          <t>알림 스트림(SSE)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>FR-016, NFR-005, NFR-006</t>
+          <t>FR-024, NFR-053</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>text/event-stream이라 응답 형식 공통 규칙의 예외. 화면은 fetch 스트림으로 받음(EventSource는 헤더를 못 붙임). 서버는 하트비트로 연결 유지</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>내부 FastAPI→Spring</t>
+          <t>내부 Spring→FastAPI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4572,12 +4613,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>/internal/transfer-requests</t>
+          <t>/internal/chat</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 생성(확인 카드용)</t>
+          <t>채팅 처리(LangGraph 구동)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4587,59 +4628,143 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+          <t>FR-014, FR-015, NFR-005, NFR-006</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 도구. 실행은 하지 않음</t>
+          <t>FastAPI 쪽 API</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>내부 Spring→FastAPI</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>/internal/details/{detailId}</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>상세 보고서 생성</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>FR-016, NFR-005, NFR-006</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI 쪽 API</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>내부 FastAPI→Spring</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>/internal/transfer-requests</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청 생성(확인 카드용)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph 도구. 실행은 하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>내부 FastAPI→Spring</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>/internal/transfers?from&amp;to&amp;cursor&amp;size</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>송금 내역·합계 조회</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Bearer(사용자 JWT 전달)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>FR-012, NFR-002, NFR-005, NFR-006</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>LangGraph 도구. 합계는 Spring 계산</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A32:H49"/>
+  <autoFilter ref="A32:H51"/>
   <mergeCells count="30">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -4682,7 +4807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8555,7 +8680,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -8592,7 +8717,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -8602,34 +8727,34 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>502</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -8639,34 +8764,34 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -8676,12 +8801,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
+          <t>data.items[].notificationId</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8691,19 +8816,19 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
+          <t>알림 ID. 화면은 마지막으로 본 ID를 기억해 새 알림을 표시(서버에 읽음 상태 없음)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
+          <t>503</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -8713,7 +8838,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -8728,19 +8853,19 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>SENT(출금) / RECEIVED(입금)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RECEIVED</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -8750,34 +8875,34 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -8787,7 +8912,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -8797,24 +8922,24 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>홍길동</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -8824,34 +8949,34 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.items[].amount</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -8861,7 +8986,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -8871,24 +8996,24 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>확정 시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>2026-10-22T10:01:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -8898,7 +9023,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -8913,19 +9038,19 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>다음 요청의 cursor(마지막 notificationId). 없으면 null</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>484</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -8935,108 +9060,96 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.hasNext</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>다음 묶음 존재 여부</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>String[]</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>Bearer {JWT}. fetch 스트림으로 보냄(EventSource는 헤더를 못 붙이고, 토큰을 URL에 넣지 않음)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -9046,34 +9159,34 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>event: notification</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>알림 한 건. data는 E-14 items[] 한 개와 같은 모양</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>{"notificationId":503,"direction":"RECEIVED",...}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -9083,7 +9196,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>: ping</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -9093,24 +9206,24 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>하트비트 주석 줄. nginx 읽기 제한보다 짧은 간격으로 보내 연결 유지</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>: ping</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -9127,7 +9240,7 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
+          <t>JWT 없음·만료·위조 — 스트림을 열기 전에 401</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
@@ -9135,7 +9248,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -9172,7 +9285,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -9182,7 +9295,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -9197,29 +9310,29 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -9234,19 +9347,19 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -9256,34 +9369,34 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -9293,34 +9406,34 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -9330,7 +9443,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -9345,79 +9458,103 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
+          <t>data.transferCard.recipientName</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
+          <t>수취인 이름</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr"/>
+          <t>data.transferCard.recipientAccountNumber</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
+          <t>수취인 계좌</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>123456789012</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.transferCard.fromAccountNumber</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9427,39 +9564,39 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
+          <t>data.transferCard.amount</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -9469,29 +9606,29 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>data.transferCard.expiresAt</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9506,56 +9643,56 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -9565,34 +9702,34 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -9602,7 +9739,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -9612,24 +9749,24 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -9639,7 +9776,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -9649,76 +9786,64 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>상세 보기 ID(분석 답변일 때)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>987654321098</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -9728,29 +9853,29 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9765,104 +9890,140 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="2" t="inlineStr"/>
+          <t>data.report</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr"/>
+          <t>상세 보고서 본문</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="2" t="inlineStr"/>
+          <t>data.table.columns</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>String[]</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
+          <t>표 머리글</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>["항목", ...]</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
+          <t>data.table.rows</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>String[][]</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr"/>
+          <t>표 행</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>[[...]]</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -9872,98 +10033,74 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>재무제표 기준·미공시 표시</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -9973,30 +10110,34 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr"/>
+          <t>Bearer {JWT}</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Bearer eyJ...</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -10006,12 +10147,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -10021,66 +10162,66 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -10095,19 +10236,19 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -10117,12 +10258,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>data.requestId</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -10132,19 +10273,19 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -10154,12 +10295,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -10169,19 +10310,19 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -10191,7 +10332,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -10206,19 +10347,19 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -10228,7 +10369,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.fromAccountNumber</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -10243,19 +10384,19 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>출금 계좌(대표 계좌)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>987654321098</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10265,12 +10406,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -10280,19 +10421,19 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -10302,12 +10443,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.expiresAt</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -10317,125 +10458,89 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2026-09-27T10:05:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27T10:01:00+09:00</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>ALIAS_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
+          <t>등록되지 않은 별칭</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10445,25 +10550,613 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Header Authorization</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Bearer {JWT}</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Bearer eyJ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Query from</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>시작일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Query to</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>종료일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Query cursor</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Query size</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>기본 20</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>data.sentTotal</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>data.receivedTotal</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>data.count</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 건수</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].transferId</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>송금 ID</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].direction</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>SENT / RECEIVED</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].counterpartName</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>상대 이름</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].counterpartAccountNumber</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>상대 계좌</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>123456789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].amount</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].createdAt</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>시각(ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:01:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>data.nextCursor</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G168"/>
+  <autoFilter ref="A1:G184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -13,9 +13,9 @@
     <sheet name="트래픽 추정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$32:$H$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항'!$A$1:$G$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API 목록'!$A$36:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API 상세'!$A$1:$G$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1646,27 +1646,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NFR-001</t>
+          <t>FR-030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>비기능</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AI 경로에 송금 실행 권한 없음</t>
+          <t>관리자 계정</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>LangGraph는 조회·송금 요청 생성까지. 실행은 사용자가 [보내기]를 누르면 Spring이 함</t>
+          <t>회원에 역할(USER·ADMIN, 기본 USER). 관리자는 가입 화면 없이 운영자가 DB에서 지정(아이디 목록 설정으로 정하면 그 아이디로 먼저 가입한 사람이 관리자가 됨). /api/v1/admin/**는 요청마다 DB의 역할을 확인해 관리자만 허용(아니면 403 ADMIN_ONLY) — JWT에 넣지 않아 역할을 바꾸면 바로 적용. 관리자 화면은 주소로 들어감(메뉴 없음)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>E-12, I-03</t>
+          <t>E-16, E-17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NFR-002</t>
+          <t>FR-031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>비기능</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LLM은 숫자를 만들지 않음</t>
+          <t>AI 사용량 관리 화면</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>돈 숫자는 Spring, DART 재무 숫자는 FastAPI 계산 코드. LLM은 받은 숫자를 설명만</t>
+          <t>관리자 화면(JSP, 렌더링은 다른 화면처럼 인증 없이·데이터는 관리자 API): 날짜별 사용자 AI 사용량(LLM 호출 수·대체 호출 수·입력·출력 토큰·비용 추정, 많이 쓴 순)과 사용자별 AI 사용 정지·해제(사유 기록). 정지는 채팅·상세 보기만 막고 송금·계좌는 그대로(NFR-003과 같은 경계)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>E-16, E-17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NFR-003</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>장애 격리</t>
+          <t>AI 경로에 송금 실행 권한 없음</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연에도 송금·계좌는 정상. 채팅만 AI_SERVER_UNAVAILABLE</t>
+          <t>LangGraph는 조회·송금 요청 생성까지. 실행은 사용자가 [보내기]를 누르면 Spring이 함</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1750,14 +1750,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-12, I-03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NFR-004</t>
+          <t>NFR-002</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1단계 내부 REST</t>
+          <t>LLM은 숫자를 만들지 않음</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Spring ↔ FastAPI 내부 REST, Spring은 RestClient(기준 수치)</t>
+          <t>돈 숫자는 Spring, DART 재무 숫자는 FastAPI 계산 코드. LLM은 받은 숫자를 설명만</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1785,12 +1785,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-003</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1800,17 +1804,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 내부 전용</t>
+          <t>장애 격리</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>/internal/** 는 Docker 내부망에서만 호출. 브라우저는 Spring만 호출</t>
+          <t>FastAPI 장애·지연에도 송금·계좌는 정상. 채팅만 AI_SERVER_UNAVAILABLE</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1820,14 +1824,14 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>I-01, I-02, I-03, I-04</t>
+          <t>E-11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>NFR-004</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1837,17 +1841,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>내부 호출 시 JWT 전달</t>
+          <t>1단계 내부 REST</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Spring → FastAPI → Spring으로 사용자 JWT를 그대로 전달하고 Spring이 본인 확인. AI가 다른 사용자 계좌에 접근 불가</t>
+          <t>Spring ↔ FastAPI 내부 REST, Spring은 RestClient(기준 수치)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1855,16 +1859,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>I-01, I-02, I-03, I-04</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NFR-007</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>인증 방식</t>
+          <t>FastAPI 내부 전용</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>JWT는 localStorage + Bearer 헤더. JSP 페이지는 인증 없이 렌더링하고 데이터는 fetch. 쿠키 미사용이라 CSRF 해당 없음</t>
+          <t>/internal/** 는 Docker 내부망에서만 호출. 브라우저는 Spring만 호출</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1892,12 +1892,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>I-01, I-02, I-03, I-04</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NFR-008</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1907,17 +1911,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>금액 타입</t>
+          <t>내부 호출 시 JWT 전달</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 단위 정수(Long)</t>
+          <t>Spring → FastAPI → Spring으로 사용자 JWT를 그대로 전달하고 Spring이 본인 확인. AI가 다른 사용자 계좌에 접근 불가</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1925,12 +1929,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>I-01, I-02, I-03, I-04</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NFR-009</t>
+          <t>NFR-007</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1940,17 +1948,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>송금</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>동시 송금 잔액 정합성</t>
+          <t>인증 방식</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>동시에 송금해도 잔액이 음수가 되거나 어긋나지 않음</t>
+          <t>JWT는 localStorage + Bearer 헤더. JSP 페이지는 인증 없이 렌더링하고 데이터는 fetch. 쿠키 미사용이라 CSRF 해당 없음</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1958,16 +1966,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>E-12</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NFR-010</t>
+          <t>NFR-008</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1977,17 +1981,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>송금</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>중복 클릭 1회 송금</t>
+          <t>금액 타입</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>요청ID 1회용 — [보내기]를 여러 번 눌러도 송금은 한 번</t>
+          <t>원 단위 정수(Long)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1995,16 +1999,12 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>E-12</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>NFR-011</t>
+          <t>NFR-009</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>범위 원칙</t>
+          <t>동시 송금 잔액 정합성</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리. 화면 스타일은 현대닷컴 톤 공통 CSS 하나만(화면별 디자인 없음). 남김: 계좌 소유자 확인, 비밀번호 해시</t>
+          <t>동시에 송금해도 잔액이 음수가 되거나 어긋나지 않음</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2032,12 +2032,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>NFR-012</t>
+          <t>NFR-010</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2047,17 +2051,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>가드레일</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>입력: 인젝션 규칙</t>
+          <t>중복 클릭 1회 송금</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
+          <t>요청ID 1회용 — [보내기]를 여러 번 눌러도 송금은 한 번</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2065,12 +2069,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NFR-013</t>
+          <t>NFR-011</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>가드레일</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>입력: 개인정보 가림</t>
+          <t>범위 원칙</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>주민·카드번호를 가린 뒤 진행(차단 아님)</t>
+          <t>제외: CSRF 방어, 페이지 보호, 입력값 검증·공통 예외 처리. 화면 스타일은 현대닷컴 톤 공통 CSS 하나만(화면별 디자인 없음). 남김: 계좌 소유자 확인, 비밀번호 해시</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2103,7 +2111,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>NFR-014</t>
+          <t>NFR-012</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2118,12 +2126,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>구조화: 송금 값 검증</t>
+          <t>입력: 인젝션 규칙</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015). 송금 발화 평가 세트(정상·누락·애매)로 금액·수취인 일치율, 되묻기 재현율, 틀린 확인 카드 수(목표 0) 측정. LLM 추출만 → 스키마 검증 → 원문 대조 순으로 하나씩 추가</t>
+          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2136,7 +2144,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NFR-015</t>
+          <t>NFR-013</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2151,12 +2159,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>검색: 공시 본문 구분</t>
+          <t>입력: 개인정보 가림</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>공시 본문을 '데이터' 구분자로 감싸서 LLM에 전달</t>
+          <t>주민·카드번호를 가린 뒤 진행(차단 아님)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2169,7 +2177,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NFR-016</t>
+          <t>NFR-014</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2184,12 +2192,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>출력: 숫자 환각 가드 1~3단계</t>
+          <t>구조화: 송금 값 검증</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>① 프롬프트만(기준선) → ② 숫자 존재 대조 → ③ 항목·값 쌍 대조. 단계마다 평가 세트로 측정(정답은 재무 테이블, 자동 채점). 근거 범위: 재무 지표 4개는 항목·값 쌍 대조, 사업의 내용 본문 숫자는 검색 조각과 존재 대조 + 출처 표시. 걸리면 guard=NUMBER_UNVERIFIED</t>
+          <t>송금 금액·수취인(계좌번호·별칭)을 스키마로 검증하고 원문과 다시 대조. 빠지거나 애매하면 되묻고, 답은 같은 대화에서 이어 받음(FR-015). 송금 발화 평가 세트(정상·누락·애매)로 금액·수취인 일치율, 되묻기 재현율, 틀린 확인 카드 수(목표 0) 측정. LLM 추출만 → 스키마 검증 → 원문 대조 순으로 하나씩 추가</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2202,7 +2210,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NFR-017</t>
+          <t>NFR-015</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2217,12 +2225,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>출력: 투자 권유 표현</t>
+          <t>검색: 공시 본문 구분</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>표현 목록으로 판정 → guard=ADVICE</t>
+          <t>공시 본문을 '데이터' 구분자로 감싸서 LLM에 전달</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2235,7 +2243,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>NFR-018</t>
+          <t>NFR-016</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2250,12 +2258,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>출력: 시스템 프롬프트 유출 감지</t>
+          <t>출력: 숫자 환각 가드 1~3단계</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK</t>
+          <t>① 프롬프트만(기준선) → ② 숫자 존재 대조 → ③ 항목·값 쌍 대조. 단계마다 평가 세트로 측정(정답은 재무 테이블, 자동 채점). 근거 범위: 재무 지표 4개는 항목·값 쌍 대조, 사업의 내용 본문 숫자는 검색 조각과 존재 대조 + 출처 표시. 걸리면 guard=NUMBER_UNVERIFIED</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2268,110 +2276,110 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>NFR-017</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>출력: 투자 권유 표현</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>표현 목록으로 판정 → guard=ADVICE</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>NFR-018</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>출력: 시스템 프롬프트 유출 감지</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>NFR-019</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>가드레일</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>공통: 차단 처리</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>걸리면 정상 응답(success=true) + 고정 문장 + 판정 코드. 가드별 행동 표. 가드는 LangGraph 노드, 걸리면 조건부 엣지로 END</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>E-11</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>NFR-020</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>가드레일</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>입력: 분류 모델</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Prompt Guard 추가 후 규칙만 쓸 때와 전후 측정(한국어 성능 확인)</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>NFR-021</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>가드레일</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>출력: 숫자 가드 4단계</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>표기 정규화(조·억·%·반올림) → 오탐 감소 측정</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>NFR-022</t>
+          <t>NFR-020</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2386,12 +2394,12 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>출력: 숫자 가드 5단계</t>
+          <t>입력: 분류 모델</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>자리표시자 구조(숫자는 코드가 채움) → 환각 구조적 0</t>
+          <t>Prompt Guard 추가 후 규칙만 쓸 때와 전후 측정(한국어 성능 확인)</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2404,7 +2412,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>NFR-023</t>
+          <t>NFR-021</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2419,12 +2427,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>검색: 공시 본문 검사</t>
+          <t>출력: 숫자 가드 4단계</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>간접 인젝션 검사</t>
+          <t>표기 정규화(조·억·%·반올림) → 오탐 감소 측정</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2435,46 +2443,42 @@
       <c r="G53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>NFR-024</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>NFR-022</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>채팅 호출 횟수 제한</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>E-11</t>
-        </is>
-      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>출력: 숫자 가드 5단계</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>자리표시자 구조(숫자는 코드가 채움) → 환각 구조적 0</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>NFR-025</t>
+          <t>NFR-023</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2484,17 +2488,17 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>가드레일</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>호출 제한 Redis 이전</t>
+          <t>검색: 공시 본문 검사</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>서버를 2대 이상으로 늘리면 카운터 공유를 위해 Redis로 이전</t>
+          <t>간접 인젝션 검사</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2507,7 +2511,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NFR-026</t>
+          <t>NFR-024</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2517,17 +2521,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>관측</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>자체 로그</t>
+          <t>채팅 호출 횟수 제한</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>판정 코드, 노드별 소요 시간을 로그 테이블에 기록</t>
+          <t>Spring에서 사용자별 제한. MVP는 메모리 카운터, 사용자당 분당 10회. 초과 시 HTTP 429 RATE_LIMITED</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2535,12 +2539,16 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>NFR-027</t>
+          <t>NFR-025</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2550,17 +2558,17 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>관측</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>LLM 추적</t>
+          <t>호출 제한 Redis 이전</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Langfuse</t>
+          <t>서버를 2대 이상으로 늘리면 카운터 공유를 위해 Redis로 이전</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2573,7 +2581,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>NFR-028</t>
+          <t>NFR-026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2583,17 +2591,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>테스트</t>
+          <t>관측</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>트래픽 추정</t>
+          <t>자체 로그</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TAM → SAM → SOM → MAU → DAU → 피크 → TPS. '트래픽 추정' 시트(수식). 피크는 개장 직후 30분 DAU의 17.2%(한국거래소 대용치), 버퍼 5배. 목표 약 93 TPS, 동시 사용자 약 992명(버퍼 약 4,960명)</t>
+          <t>판정 코드, 노드별 소요 시간을 로그 테이블에 기록</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2604,42 +2612,42 @@
       <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>NFR-029</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>NFR-027</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>LLM 지연 실측</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>실제 OpenAI로 지연을 재서 p50·p95·분포 기록. 가짜 LLM은 이 실측 분포를 그대로 재현(시드 고정)</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>관측</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>LLM 추적</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Langfuse</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NFR-030</t>
+          <t>NFR-028</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2654,12 +2662,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>성능 테스트(API 단위)</t>
+          <t>트래픽 추정</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록: 전체 조회 → 오프셋 → 커서. p95 &lt; 500ms</t>
+          <t>TAM → SAM → SOM → MAU → DAU → 피크 → TPS. '트래픽 추정' 시트(수식). 피크는 개장 직후 30분 DAU의 17.2%(한국거래소 대용치), 버퍼 5배. 목표 약 93 TPS, 동시 사용자 약 992명(버퍼 약 4,960명)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2672,7 +2680,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>NFR-031</t>
+          <t>NFR-029</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2687,12 +2695,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>부하 테스트(전체 시나리오)</t>
+          <t>LLM 지연 실측</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>행동 유형 4개(DART 50%·송금 30%·내역 15%·가입 5%) 비율로 목표 TPS 유지, 가짜 LLM. 합격: 일반 API p95 &lt; 500ms, 채팅 p95 &lt; 가짜 지연 p95 + 1초, 에러율 &lt; 1%</t>
+          <t>실제 OpenAI로 지연을 재서 p50·p95·분포 기록. 가짜 LLM은 이 실측 분포를 그대로 재현(시드 고정)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2705,7 +2713,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>NFR-032</t>
+          <t>NFR-030</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2720,12 +2728,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>스트레스 테스트</t>
+          <t>성능 테스트(API 단위)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>약 4,960 VU부터 무너질 때까지 늘려 한계점 기록(최소 DAU 전원 동시 34,608명까지 확인), 가짜 LLM. 한계 TPS로 버틸 수 있는 최대 피크 집중도 역산</t>
+          <t>송금 내역 목록: 전체 조회 → 오프셋 → 커서. p95 &lt; 500ms</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2738,7 +2746,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>NFR-033</t>
+          <t>NFR-031</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2753,12 +2761,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>로드맵 비교(API 단위)</t>
+          <t>부하 테스트(전체 시나리오)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지: REST(RestClient) → 비동기(WebClient) 단계별 처리량·스레드 비교, 가짜 LLM</t>
+          <t>행동 유형 4개(DART 50%·송금 30%·내역 15%·가입 5%) 비율로 목표 TPS 유지, 가짜 LLM. 합격: 일반 API p95 &lt; 500ms, 채팅 p95 &lt; 가짜 지연 p95 + 1초, 에러율 &lt; 1%</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2771,7 +2779,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NFR-034</t>
+          <t>NFR-032</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2786,12 +2794,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>정합성 테스트(API 단위)</t>
+          <t>스트레스 테스트</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0. 락 없는 버전(기준선)·FOR UPDATE·@Version과 위반 건수·TPS 비교(측정 브랜치에서만)</t>
+          <t>약 4,960 VU부터 무너질 때까지 늘려 한계점 기록(최소 DAU 전원 동시 34,608명까지 확인), 가짜 LLM. 한계 TPS로 버틸 수 있는 최대 피크 집중도 역산</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2804,7 +2812,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>NFR-035</t>
+          <t>NFR-033</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2819,12 +2827,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>실제 OpenAI 검증</t>
+          <t>로드맵 비교(API 단위)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>전체 시나리오를 목표 TPS의 10%로 5분. 판정 없이 기록. OpenAI 429는 우리 에러와 분리 집계, 재시도 없음, 실행 전 예상 비용 기록</t>
+          <t>채팅 메시지: REST(RestClient) → 비동기(WebClient) 단계별 처리량·스레드 비교, 가짜 LLM</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2837,7 +2845,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>NFR-036</t>
+          <t>NFR-034</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2852,12 +2860,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>정합성 테스트(API 단위)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Prometheus: Spring·FastAPI(HTTP 지연, Tomcat 스레드, DB 커넥션 풀, LLM 호출 시간, OpenAI 에러 수, 가드 판정 횟수), PostgreSQL(커넥션, 락 대기), cAdvisor(컨테이너 CPU·메모리), k6 remote write → Grafana 한 화면</t>
+          <t>송금 확정 동시 요청(같은 요청ID 연타, 같은 계좌 동시 출금) 후 SQL 3개: 전체 잔액 합계 불변 / 중복 확정 0 / 음수 잔액 0. 락 없는 버전(기준선)·FOR UPDATE·@Version과 위반 건수·TPS 비교(측정 브랜치에서만)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -2870,7 +2878,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>NFR-037</t>
+          <t>NFR-035</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2885,12 +2893,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>측정 환경</t>
+          <t>실제 OpenAI 검증</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>앱(Spring·FastAPI·PostgreSQL)만 AWS t3.small 사양으로 제한, k6·Prometheus·Grafana는 제한 밖</t>
+          <t>전체 시나리오를 목표 TPS의 10%로 5분. 판정 없이 기록. OpenAI 429는 우리 에러와 분리 집계, 재시도 없음, 실행 전 예상 비용 기록</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2901,42 +2909,42 @@
       <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NFR-038</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>NFR-036</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>테스트</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>스파이크·내구 테스트</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>장 마감 직후 급증, 장시간 유지</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>모니터링</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus: Spring·FastAPI(HTTP 지연, Tomcat 스레드, DB 커넥션 풀, LLM 호출 시간, OpenAI 에러 수, 가드 판정 횟수), PostgreSQL(커넥션, 락 대기), cAdvisor(컨테이너 CPU·메모리), k6 remote write → Grafana 한 화면</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>NFR-039</t>
+          <t>NFR-037</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2946,17 +2954,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>품질</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>RAG 검색 품질 측정</t>
+          <t>측정 환경</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>평가 세트(질문–정답 청크)로 Recall@5·MRR 측정, 청킹·검색 방식 비교. 벡터 검색으로 시작하고, BM25(RRF)·재순위는 지표로 문제가 확인되면 비교 후 도입</t>
+          <t>앱(Spring·FastAPI·PostgreSQL)만 AWS t3.small 사양으로 제한, k6·Prometheus·Grafana는 제한 밖</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -2969,209 +2977,209 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
+          <t>NFR-038</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>스파이크·내구 테스트</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>장 마감 직후 급증, 장시간 유지</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>NFR-039</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>RAG 검색 품질 측정</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>평가 세트(질문–정답 청크)로 Recall@5·MRR 측정, 청킹·검색 방식 비교. 벡터 검색으로 시작하고, BM25(RRF)·재순위는 지표로 문제가 확인되면 비교 후 도입</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>NFR-040</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>로드맵</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2단계 비동기 전환</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>WebClient. Java 17이라 가상 스레드 불가 → LLM 대기 중 스레드 반납, 동시 처리량 비교</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>추후</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>NFR-042</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>로드맵</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>3단계 MCP</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>송금·계좌 도구(조회·요청 생성·예약 송금 초안까지, 실행 권한 없음), DART 검색 도구. 에이전트 호출은 입장 제어(NFR-049)로 보호</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>추후</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>NFR-043</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>테스트</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>계좌 동시성 정합성</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>동시 계좌 개설(같은/다른 Idempotency-Key), 동시 대표 계좌 변경 후 확인: 대표 계좌 항상 1개, 멱등키 재사용 시 신규 계좌 미생성. 실제 PostgreSQL(Testcontainers)로 검증(목·가짜 DB 사용 안 함)</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>E-03, E-05</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>NFR-044</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>품질</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>질문 인식 측정</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>평가 세트로 의도 분류 정확도(재무·본문·송금·내역)와 기업명 인식률(삼전 같은 구어 표현 포함) 측정. 정식 기업명 일치로 시작하고, 별칭 사전·오타 허용은 인식률 문제가 확인되면 도입</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>NFR-045</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>알림 대량 전달</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>송금 확정 → 알림 도착 p95 &lt; 1초(접속 중 사용자). 동시 접속 1천 → 1만으로 늘려 노드 하나의 한계(연결 수·초당 전달 수)를 재고 100만 명은 노드 수로 역산. 외부 푸시(FCM 기본 한도 분당 60만 건)는 1초 목표에서 제외. 알림 발송이 확정 p95를 늘리지 않는지 함께 확인</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>NFR-046</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>내역 집계 조회 성능</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>내역 100만 건 계정에서 추이 조회 p95 &lt; 500ms(기간 1개월·1년·전체). (계좌, 시각) 복합 인덱스 집계 → 일별 요약 테이블 순으로 하나씩 바꿔 측정(NFR-030과 같은 시드·도구). 파티셔닝은 테이블 전체가 수억 행일 때만, 샤딩은 하지 않음(송금 하나가 두 샤드에 걸치면 한 트랜잭션으로 못 묶음)</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>NFR-047</t>
+          <t>NFR-045</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3181,17 +3189,17 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>품질</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>AI 시나리오 테스트</t>
+          <t>알림 대량 전달</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>LLM이 사용자 역할(처음 쓰는 사람·급한 사람·오타·말 바꾸기)로 채팅 시나리오를 만들어 실제 API로 끝까지 진행. 합격은 규칙으로: 틀린 확인 카드 0, 턴 응답이 읽기 제한 안, 같은 되묻기 2회 이하, 내부 오류 문구 노출 0. LLM 판정은 이상 후보 표시만(사람이 확인). 실행 전 예상 비용 기록, 같은 세트 3회</t>
+          <t>송금 확정 → 알림 도착 p95 &lt; 1초(접속 중 사용자). 동시 접속 1천 → 1만으로 늘려 노드 하나의 한계(연결 수·초당 전달 수)를 재고 100만 명은 노드 수로 역산. 외부 푸시(FCM 기본 한도 분당 60만 건)는 1초 목표에서 제외. 알림 발송이 확정 p95를 늘리지 않는지 함께 확인</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3204,7 +3212,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>NFR-048</t>
+          <t>NFR-046</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3214,17 +3222,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>외부 연동 장애·배치 지연 대응</t>
+          <t>내역 집계 조회 성능</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>외부 API(DART·OpenAI·외부 이체망) 오류를 일시·한도·점검·영구로 나눠 처리: 일시 오류만 재시도(지수 백오프 + 지터), 응답 없는 쓰기는 재전송 대신 조회로 확인, 연속 실패는 차단기로 멈춤. 예약 송금이 한 시각에 몰리면 실행 시각 분산·워커 분할(SKIP LOCKED)·진행 상태 표시, 하루 마감 대사(NFR-034 SQL 3개). 외부 이체망은 가짜 서버로 장애 주입</t>
+          <t>내역 100만 건 계정에서 추이 조회 p95 &lt; 500ms(기간 1개월·1년·전체). (계좌, 시각) 복합 인덱스 집계 → 일별 요약 테이블 순으로 하나씩 바꿔 측정(NFR-030과 같은 시드·도구). 파티셔닝은 테이블 전체가 수억 행일 때만, 샤딩은 하지 않음(송금 하나가 두 샤드에 걸치면 한 트랜잭션으로 못 묶음)</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3237,7 +3245,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>NFR-049</t>
+          <t>NFR-047</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3247,17 +3255,17 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>품질</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>수평 확장·급증 대응</t>
+          <t>AI 시나리오 테스트</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1대 한계(15 TPS, 피크 30분 약 4,800명)를 넘으면 순서대로: ① 입장 제어(사용자·API 키별 한도, 동시 처리 상한, 넘치면 429 + Retry-After, 송금 확정 우선, 쓰기 도구 멱등 키) ② 무상태화(대화 상태 PostgreSQL, 호출 제한·캐시 Redis, 알림 SSE는 연결이 다른 서버에 있어도 닿게 Redis pub/sub) ③ nginx(NFR-053) 뒤 FastAPI·Spring 여러 대(FastAPI부터), DB 커넥션 풀러 ④ LLM 토큰 예산. 1 → 2 → 4대에서 같은 stress.sh로 한계 TPS 비교</t>
+          <t>LLM이 사용자 역할(처음 쓰는 사람·급한 사람·오타·말 바꾸기)로 채팅 시나리오를 만들어 실제 API로 끝까지 진행. 합격은 규칙으로: 틀린 확인 카드 0, 턴 응답이 읽기 제한 안, 같은 되묻기 2회 이하, 내부 오류 문구 노출 0. LLM 판정은 이상 후보 표시만(사람이 확인). 실행 전 예상 비용 기록, 같은 세트 3회</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3270,7 +3278,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>NFR-050</t>
+          <t>NFR-048</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3280,17 +3288,17 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>홈서버 망 분리·접근 통제</t>
+          <t>외부 연동 장애·배치 지연 대응</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Docker 네트워크를 앞단(터널 커넥터 ↔ nginx ↔ Spring)·내부(Spring·FastAPI·DB)·외부 호출(터널 커넥터·FastAPI·collector만 인터넷으로)로 분리 — Spring·DB는 인터넷으로 못 나감. 들어오는 포트 0(터널로 웹 공개 — NFR-053의 80·443 포트포워딩을 대체), 관리(SSH·Grafana·DB)와 배포는 VPN(사람·기기 단위 허용)으로만. 호스트 방화벽 기본 차단, Docker 포트는 127.0.0.1에만. 앱별 DB 계정(최소 권한)</t>
+          <t>외부 API(DART·OpenAI·외부 이체망) 오류를 일시·한도·점검·영구로 나눠 처리: 일시 오류만 재시도(지수 백오프 + 지터), 응답 없는 쓰기는 재전송 대신 조회로 확인, 연속 실패는 차단기로 멈춤. 예약 송금이 한 시각에 몰리면 실행 시각 분산·워커 분할(SKIP LOCKED)·진행 상태 표시, 하루 마감 대사(NFR-034 SQL 3개). 외부 이체망은 가짜 서버로 장애 주입</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3303,112 +3311,322 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
+          <t>NFR-049</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>수평 확장·급증 대응</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>1대 한계(15 TPS, 피크 30분 약 4,800명)를 넘으면 순서대로: ① 입장 제어(사용자·API 키별 한도, 동시 처리 상한, 넘치면 429 + Retry-After, 송금 확정 우선, 쓰기 도구 멱등 키) ② 무상태화(대화 상태 PostgreSQL, 호출 제한·캐시 Redis, 알림 SSE는 연결이 다른 서버에 있어도 닿게 Redis pub/sub) ③ nginx(NFR-053) 뒤 FastAPI·Spring 여러 대(FastAPI부터), DB 커넥션 풀러 ④ LLM 토큰 예산(계정 전체 — 사용자별 하루 한도는 NFR-054). 1 → 2 → 4대에서 같은 stress.sh로 한계 TPS 비교</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>NFR-050</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>홈서버 망 분리·접근 통제</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Docker 네트워크를 앞단(터널 커넥터 ↔ nginx ↔ Spring)·내부(Spring·FastAPI·DB)·외부 호출(터널 커넥터·FastAPI·collector만 인터넷으로)로 분리 — Spring·DB는 인터넷으로 못 나감. 들어오는 포트 0(터널로 웹 공개 — NFR-053의 80·443 포트포워딩을 대체), 관리(SSH·Grafana·DB)와 배포는 VPN(사람·기기 단위 허용)으로만. 호스트 방화벽 기본 차단, Docker 포트는 127.0.0.1에만. 앱별 DB 계정(최소 권한)</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
           <t>NFR-051</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>홈서버 운영 점검</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>공개 전·분기마다: 네트워크(공인 IP·CGNAT·DDNS·업로드 대역폭·ISP 약관), 미들웨어(타임아웃 사슬, 로그 크기 제한, 재시작 정책·헬스체크), OS(보안 업데이트, 시간 동기, 디스크·메모리 경고, SSH 키 전용), DB(매일 백업 + 다른 곳 보관 + 복구 리허설, 커넥션 합 ≤ max_connections, 슬로우 쿼리 로그)</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>추후</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>NFR-052</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>품질</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>사업의 내용 재검색(LangGraph 루프)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>사업의 내용 답변에 근거 없는 숫자가 있으면(NUMBER_UNVERIFIED 조건) 질문을 검색어로 고쳐 써서 한 번 더 검색·답변. 최대 1회, 판정은 코드. 고친 검색어는 검색에만 쓴다. 지연(재검색 턴은 10초 읽기 제한 초과 예상)은 우선 그대로 두고 재검색 비율·재검색 후 통과율·턴 지연을 잰 뒤 개선</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>E-11</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>NFR-053</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>리버스 프록시·HTTPS(nginx)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>도메인을 붙이고 nginx를 유일한 입구로: TLS 종료(Let's Encrypt, 자동 갱신), 80은 443으로 넘김, Spring으로 프록시(X-Forwarded-For·Proto 전달). 공유기는 80·443만 nginx로 넘기고 Spring 8080은 공개 중단(127.0.0.1에만). 타임아웃은 nginx &gt; Spring 읽기 제한(채팅 10초·상세 30초), 알림 스트림(E-15)은 버퍼링 끄고 하트비트 간격보다 길게. 로그인·가입은 IP별 요청 제한(limit_req). 부하 측정 환경은 지금처럼 Spring 직접(기준선 유지)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>E-01, E-02, E-15</t>
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>NFR-054</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>AI 게이트웨이: 사용량 기록·하루 한도</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>LLM 호출이 모두 지나는 FastAPI 한 곳(게이트웨이)이 호출마다 사용자·모델·입력·출력 토큰·대체 여부를 사용량 테이블에 기록 — Spring이 10초에 끊은 턴도 빠지지 않게 FastAPI가 씀. Spring은 채팅·상세 보기 전에 확인: 관리자 정지면 403 AI_BLOCKED, 오늘(KST) 합계가 하루 한도 이상이면 429 AI_QUOTA_EXCEEDED(자정에 풀림). 기본 한도 50만 토큰 ≈ $0.07(실측 평균 호출당 2,079토큰이면 약 240회). 확인 뒤 기록이라 마지막 한 턴만큼 넘을 수 있음. Prometheus에는 모델별 합계만(사용자별은 시계열이 사용자 수만큼 늘어 DB에서 집계)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>E-11, E-13, E-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>NFR-055</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>가드레일</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>AI 게이트웨이: 개인정보 제거·가명화</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>NFR-013(주민·카드번호 가림)을 넓힘. LLM이 값을 알아야 하는지로 나눔: 필요 없음(주민·카드·전화번호·이메일) → 제거(자리표시자로 바꾸고 되돌리지 않음). 가리켜야 함(수취인 계좌번호) → 가명화([계좌1]로 보내고 송금 요청 도구 직전에 코드가 되돌림, 대응표는 서버의 대화 상태에만). 탐지가 어려움(실명) → 구조로 피함(송금은 별칭·계좌번호로만 받고, 코드가 만든 답변(확인 문장·내역)의 실명은 대화 기록에 자리표시자로 남겨 다음 LLM 호출에 안 실림). 개인정보 문장 세트로 LLM에 간 원문 0건·오탐률, 송금 발화 세트(NFR-014) 일치율 유지 확인</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>E-11, I-01, I-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>NFR-056</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>AI 게이트웨이: 장애 대체(Claude)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 호출이 오류(5xx·429·연결 실패)나 타임아웃이면 같은 요청을 Claude로 1번 더(LangChain with_fallbacks + langchain-anthropic. Anthropic의 OpenAI 호환 엔드포인트는 시험·비교용이라 쓰지 않음). 모델은 설정값, 기본 Claude Haiku 5.5(가장 빠른 급, 강제 도구 호출 지원). 타임아웃은 호출 종류별 실측 p95 + 여유로 두고 대체 호출에도 둠(지금은 LLM 호출에 타임아웃이 없음). 대체 경로에도 NFR-055를 거친 입력만. 구조화 출력은 LangChain이 공급자별 기본 방식으로 맞춤(OpenAI json_schema, Claude 도구 호출). 임베딩은 대체하지 않음(Anthropic에는 임베딩 모델이 없고, 다른 모델 벡터는 기존 색인과 못 섞음) → OpenAI 장애 때 사업의 내용 질문은 안내 문장, 대체 방법은 NFR-057. 어느 모델이 답했는지 기록. 가짜 LLM에 오류·지연을 넣어 대체율·턴 p95 측정</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>E-11, E-13, I-01, I-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>NFR-057</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>AI 게이트웨이 확장</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>차단기(연속 실패면 OpenAI를 건너뛰고 바로 대체, 회복 확인 뒤 복귀), 대체 모델 품질 평가(같은 평가 세트로 의도 인식률·숫자 가드 통과율 비교), 임베딩 대체(PostgreSQL 키워드 검색 또는 다른 공급자 임베딩으로 만든 두 번째 색인 — 본문 검색 평가 세트(NFR-039)로 Recall@5 비교), 공급자 추가(Gemini 등, 우선순위·비용 기준), 사용자별 한도 조정·예산 알림, 이름 탐지(한국어 NER — 탐지율·오탐률을 재고 도입), 별도 게이트웨이 서비스(LiteLLM 등)는 여러 서비스가 LLM 키를 나눠 쓸 때</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>추후</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G82"/>
+  <autoFilter ref="A1:G88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3419,7 +3637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3847,17 +4065,19 @@
       <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>guard 코드</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN_ONLY</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>관리자 전용 API — 역할이 ADMIN이 아님</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
@@ -3867,15 +4087,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
+          <t>MEMBER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>회원 없음</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
@@ -3885,15 +4107,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n"/>
+          <t>AI_BLOCKED</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>관리자가 AI 사용을 정지한 사용자 — 채팅·상세 보기만 실패, 송금·계좌는 정상</t>
+        </is>
+      </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
@@ -3903,15 +4127,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NUMBER_UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n"/>
+          <t>AI_QUOTA_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>오늘(KST) AI 사용 한도 초과 — 자정에 풀림</t>
+        </is>
+      </c>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
@@ -3919,14 +4145,14 @@
       <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ADVICE</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>출력 교체 — 투자 권유 표현</t>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>guard 코드</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>설명</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
@@ -3939,12 +4165,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PROMPT_LEAK</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
@@ -3954,209 +4180,125 @@
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="10" t="n"/>
     </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>입력 차단 — 프롬프트 인젝션 대표 유형. LLM 미호출, 고정 문장</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>API ID</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>인증</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>요구사항 ID</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>NUMBER_UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>출력 교체 — 근거(재무 테이블)에 없는 숫자</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>ADVICE</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/auth/signup</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>회원가입</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>FR-001</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t>출력 교체 — 투자 권유 표현</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>PROMPT_LEAK</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/auth/login</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>FR-002</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/accounts</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>가상계좌 개설</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Bearer</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>FR-003, FR-004</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
-        </is>
-      </c>
-    </row>
+          <t>출력 교체 — 시스템 프롬프트 카나리 단어 노출</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>E-04</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/accounts</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>내 계좌·잔액 조회</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Bearer</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>API ID</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>요구사항 ID</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4166,27 +4308,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/primary</t>
+          <t>/api/v1/auth/signup</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 변경</t>
+          <t>회원가입</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Bearer</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>FR-004</t>
+          <t>FR-001</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -4194,7 +4336,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4209,22 +4351,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/charge</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>충전</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Bearer</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>FR-005</t>
+          <t>FR-002</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -4232,7 +4374,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4247,12 +4389,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/aliases</t>
+          <t>/api/v1/accounts</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>별칭 등록</t>
+          <t>가상계좌 개설</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4262,15 +4404,19 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>FR-007</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
+          <t>FR-003, FR-004</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4285,12 +4431,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/aliases</t>
+          <t>/api/v1/accounts</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>별칭 목록</t>
+          <t>내 계좌·잔액 조회</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -4300,7 +4446,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>FR-008</t>
+          <t>FR-006</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -4308,7 +4454,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4318,17 +4464,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfers?cursor&amp;size</t>
+          <t>/api/v1/accounts/{accountId}/primary</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록</t>
+          <t>대표 계좌 변경</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -4338,19 +4484,15 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>FR-011</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
-        </is>
-      </c>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4365,12 +4507,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads</t>
+          <t>/api/v1/accounts/{accountId}/charge</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>새 대화</t>
+          <t>충전</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4380,7 +4522,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>FR-013</t>
+          <t>FR-005</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -4388,7 +4530,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4403,12 +4545,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads/{threadId}/messages</t>
+          <t>/api/v1/aliases</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지</t>
+          <t>별칭 등록</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4418,19 +4560,15 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Spring이 I-01 호출. 호출 제한 적용</t>
-        </is>
-      </c>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4440,17 +4578,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
+          <t>/api/v1/aliases</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>송금 확정([보내기])</t>
+          <t>별칭 목록</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4460,19 +4598,15 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FR-010, FR-024, NFR-001, NFR-009, NFR-010</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음. 확정 트랜잭션에 알림 행 저장(FR-024)</t>
-        </is>
-      </c>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -4487,12 +4621,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/details/{detailId}</t>
+          <t>/api/v1/transfers?cursor&amp;size</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>송금 내역 목록</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -4502,19 +4636,19 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>FR-016, FR-019</t>
+          <t>FR-011</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Spring이 I-02 호출</t>
+          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4524,17 +4658,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/notifications?cursor&amp;size</t>
+          <t>/api/v1/chat/threads</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>새 대화</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4544,19 +4678,15 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FR-024</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>최신순 커서(E-09와 같은 규칙). 스트림이 끊긴 사이 놓친 알림을 채움</t>
-        </is>
-      </c>
+          <t>FR-013</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4566,17 +4696,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/stream</t>
+          <t>/api/v1/chat/threads/{threadId}/messages</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>알림 스트림(SSE)</t>
+          <t>채팅 메시지</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4586,24 +4716,24 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>FR-024, NFR-053</t>
+          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024, NFR-054, NFR-055, NFR-056</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>text/event-stream이라 응답 형식 공통 규칙의 예외. 화면은 fetch 스트림으로 받음(EventSource는 헤더를 못 붙임). 서버는 하트비트로 연결 유지</t>
+          <t>Spring이 I-01 호출. 호출 제한·AI 사용 정지·하루 한도 확인</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4613,39 +4743,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>/internal/chat</t>
+          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>채팅 처리(LangGraph 구동)</t>
+          <t>송금 확정([보내기])</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, NFR-005, NFR-006</t>
+          <t>FR-010, FR-024, NFR-001, NFR-009, NFR-010</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음. 확정 트랜잭션에 알림 행 저장(FR-024)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4655,136 +4785,388 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>/internal/details/{detailId}</t>
+          <t>/api/v1/chat/details/{detailId}</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 생성</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>FR-016, NFR-005, NFR-006</t>
+          <t>FR-016, FR-019, NFR-054, NFR-056</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API</t>
+          <t>Spring이 I-02 호출. AI 사용 정지·하루 한도 확인</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>내부 FastAPI→Spring</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>/internal/transfer-requests</t>
+          <t>/api/v1/notifications?cursor&amp;size</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 생성(확인 카드용)</t>
+          <t>알림 목록</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>FR-009, NFR-001, NFR-005, NFR-006</t>
+          <t>FR-024</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 도구. 실행은 하지 않음</t>
+          <t>최신순 커서(E-09와 같은 규칙). 스트림이 끊긴 사이 놓친 알림을 채움</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>E-15</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>외부</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/stream</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>알림 스트림(SSE)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Bearer</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>FR-024, NFR-053</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>text/event-stream이라 응답 형식 공통 규칙의 예외. 화면은 fetch 스트림으로 받음(EventSource는 헤더를 못 붙임). 서버는 하트비트로 연결 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>E-16</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>외부</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/ai-usage?date</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>사용자별 AI 사용량</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(관리자)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>FR-030, FR-031, NFR-054</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>많이 쓴 순. 날짜가 없으면 오늘(KST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>E-17</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>외부</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/members/{memberId}/ai-block</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>AI 사용 정지·해제</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(관리자)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>FR-030, FR-031</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>다음 채팅부터 적용. 송금·계좌는 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>내부 Spring→FastAPI</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>/internal/chat</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>채팅 처리(LangGraph 구동)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>FR-014, FR-015, NFR-005, NFR-006, NFR-054, NFR-055, NFR-056</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI 쪽 API. 개인정보를 지우거나 가명화한 뒤 그래프에 넣고, LLM 호출마다 사용량 기록(사용자는 전달받은 JWT의 sub — Spring이 확인한 토큰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>내부 Spring→FastAPI</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>/internal/details/{detailId}</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>상세 보고서 생성</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>FR-016, NFR-005, NFR-006, NFR-054, NFR-056</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI 쪽 API. LLM 호출마다 사용량 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>내부 FastAPI→Spring</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>/internal/transfer-requests</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청 생성(확인 카드용)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>FR-009, NFR-001, NFR-005, NFR-006, NFR-055</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph 도구. 실행은 하지 않음. 가명화한 계좌번호([계좌1])는 부르기 직전에 원래 번호로 되돌림</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>내부 FastAPI→Spring</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>/internal/transfers?from&amp;to&amp;cursor&amp;size</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>송금 내역·합계 조회</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Bearer(사용자 JWT 전달)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>FR-012, NFR-002, NFR-005, NFR-006</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>LangGraph 도구. 합계는 Spring 계산</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A32:H51"/>
-  <mergeCells count="30">
+  <autoFilter ref="A36:H57"/>
+  <mergeCells count="34">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B30:H30"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C18:H18"/>
@@ -4793,9 +5175,13 @@
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="C20:H20"/>
-    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4807,7 +5193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7875,76 +8261,52 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_BLOCKED</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>관리자가 AI 사용을 정지한 사용자</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Path requestId</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_QUOTA_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>확인 카드의 요청ID</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>tr_7f3a...</t>
-        </is>
-      </c>
+          <t>오늘(KST) AI 사용 한도 초과 — 자정에 풀림</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7959,7 +8321,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -7974,12 +8336,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌 비밀번호(숫자 4자리)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>••••</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -7991,17 +8353,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>data.transferId</t>
+          <t>Path requestId</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -8011,12 +8373,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>확인 카드의 요청ID</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
@@ -8028,12 +8390,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>password</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -8048,12 +8410,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>출금 계좌 비밀번호(숫자 4자리)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>••••</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8432,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.transferId</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -8085,12 +8447,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8469,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.recipientName</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -8122,12 +8484,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8506,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>data.balanceAfter</t>
+          <t>data.amount</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -8159,12 +8521,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>송금 후 잔액(원)</t>
+          <t>금액(원)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -8176,22 +8538,34 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr"/>
+          <t>data.fromAccountNumber</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
+          <t>출금 계좌</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>987654321098</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -8201,22 +8575,34 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>data.balanceAfter</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 없음(또는 남의 요청)</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>송금 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8231,14 +8617,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_EXPIRED</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 5분 만료</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -8256,14 +8642,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER_REQUEST_ALREADY_USED</t>
+          <t>TRANSFER_REQUEST_NOT_FOUND</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>이미 쓴 송금 요청(확정됨 또는 비밀번호 오류로 폐기)</t>
+          <t>송금 요청 없음(또는 남의 요청)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
@@ -8281,14 +8667,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_OWNED</t>
+          <t>TRANSFER_REQUEST_EXPIRED</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>내 계좌가 아님</t>
+          <t>송금 요청 5분 만료</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -8306,14 +8692,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_PASSWORD_INVALID</t>
+          <t>TRANSFER_REQUEST_ALREADY_USED</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>계좌 비밀번호 불일치 — 송금 요청ID도 폐기</t>
+          <t>이미 쓴 송금 요청(확정됨 또는 비밀번호 오류로 폐기)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
@@ -8331,14 +8717,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_BALANCE</t>
+          <t>ACCOUNT_NOT_OWNED</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족</t>
+          <t>내 계좌가 아님</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
@@ -8346,76 +8732,52 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ACCOUNT_PASSWORD_INVALID</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>계좌 비밀번호 불일치 — 송금 요청ID도 폐기</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>INSUFFICIENT_BALANCE</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>답변의 detailId</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>dt_91c2...</t>
-        </is>
-      </c>
+          <t>잔액 부족</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -8425,12 +8787,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -8445,12 +8807,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8824,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -8482,12 +8844,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문(클릭할 때 생성)</t>
+          <t>답변의 detailId</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8504,27 +8866,27 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
@@ -8541,27 +8903,27 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>상세 보고서 본문(클릭할 때 생성)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8578,12 +8940,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -8593,12 +8955,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
@@ -8610,22 +8972,34 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="2" t="inlineStr"/>
+          <t>data.table.rows</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>String[][]</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
+          <t>표 행</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>[[...]]</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8635,22 +9009,34 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
-      <c r="E113" s="2" t="inlineStr"/>
+          <t>data.table.note</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
+          <t>재무제표 기준·미공시 표시</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>연결 기준</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8665,14 +9051,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>AI_SERVER_UNAVAILABLE</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -8680,150 +9066,102 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>AI_SERVER_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
+          <t>FastAPI 장애·지연 — 채팅만 실패, 송금·계좌는 정상(장애 격리)</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>AI_BLOCKED</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>묶음 크기(기본 20)</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>관리자가 AI 사용을 정지한 사용자</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>data.items[].notificationId</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AI_QUOTA_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>알림 ID. 화면은 마지막으로 본 ID를 기억해 새 알림을 표시(서버에 읽음 상태 없음)</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
+          <t>오늘(KST) AI 사용 한도 초과 — 자정에 풀림</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8833,12 +9171,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -8853,12 +9191,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>SENT(출금) / RECEIVED(입금)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>RECEIVED</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
@@ -8870,12 +9208,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>Query cursor</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -8885,17 +9223,17 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>이전 응답의 nextCursor. 없으면 최신부터</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>502</t>
         </is>
       </c>
     </row>
@@ -8907,32 +9245,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>Query size</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>묶음 크기(기본 20)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>홍길동</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -8949,7 +9287,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
+          <t>data.items[].notificationId</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -8964,12 +9302,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>알림 ID. 화면은 마지막으로 본 ID를 기억해 새 알림을 표시(서버에 읽음 상태 없음)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>503</t>
         </is>
       </c>
     </row>
@@ -8986,7 +9324,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>data.items[].direction</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -9001,12 +9339,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>확정 시각(ISO-8601)</t>
+          <t>SENT(출금) / RECEIVED(입금)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T10:01:00+09:00</t>
+          <t>RECEIVED</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9361,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>data.items[].transferId</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -9033,17 +9371,17 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 notificationId). 없으면 null</t>
+          <t>송금 ID</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -9060,12 +9398,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>data.items[].counterpartName</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -9075,12 +9413,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>상대 이름</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>홍길동</t>
         </is>
       </c>
     </row>
@@ -9092,37 +9430,49 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
+          <t>data.items[].amount</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.items[].createdAt</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -9137,19 +9487,19 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}. fetch 스트림으로 보냄(EventSource는 헤더를 못 붙이고, 토큰을 URL에 넣지 않음)</t>
+          <t>확정 시각(ISO-8601)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>2026-10-22T10:01:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -9159,34 +9509,34 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>event: notification</t>
+          <t>data.nextCursor</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>알림 한 건. data는 E-14 items[] 한 개와 같은 모양</t>
+          <t>다음 요청의 cursor(마지막 notificationId). 없으면 null</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>{"notificationId":503,"direction":"RECEIVED",...}</t>
+          <t>484</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -9196,12 +9546,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>: ping</t>
+          <t>data.hasNext</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -9211,19 +9561,19 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>하트비트 주석 줄. nginx 읽기 제한보다 짧은 간격으로 보내 연결 유지</t>
+          <t>다음 묶음 존재 여부</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>: ping</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -9240,7 +9590,7 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조 — 스트림을 열기 전에 401</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
@@ -9248,7 +9598,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -9273,7 +9623,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>Bearer {JWT}. fetch 스트림으로 보냄(EventSource는 헤더를 못 붙이고, 토큰을 URL에 넣지 않음)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -9285,22 +9635,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>threadId</t>
+          <t>event: notification</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -9310,29 +9660,29 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>대화 ID(체크포인터 키)</t>
+          <t>알림 한 건. data는 E-14 items[] 한 개와 같은 모양</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>th_5b21...</t>
+          <t>{"notificationId":503,"direction":"RECEIVED",...}</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>: ping</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -9347,66 +9697,54 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>사용자 메시지</t>
+          <t>하트비트 주석 줄. nginx 읽기 제한보다 짧은 간격으로 보내 연결 유지</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>엄마한테 1만원 보내줘</t>
+          <t>: ping</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>data.reply</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>요약 답변. 가드에 걸리면 고정 문장</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>삼성전자 2분기 영업이익은 ...</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조 — 스트림을 열기 전에 401</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>data.guard</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -9421,29 +9759,29 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>Bearer {JWT}(관리자)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.requestId</t>
+          <t>Query date</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -9458,19 +9796,19 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>날짜(yyyy-MM-dd, KST). 없으면 오늘</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -9480,34 +9818,34 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientName</t>
+          <t>data.dailyLimitTokens</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>하루 한도(토큰, 설정값)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -9517,34 +9855,34 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.recipientAccountNumber</t>
+          <t>data.items[].memberId</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>회원 ID</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -9554,7 +9892,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.fromAccountNumber</t>
+          <t>data.items[].loginId</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -9564,24 +9902,24 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>아이디</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>jinho01</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -9591,34 +9929,34 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.amount</t>
+          <t>data.items[].calls</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>LLM 호출 수</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>212</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -9628,34 +9966,34 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>data.transferCard.expiresAt</t>
+          <t>data.items[].fallbackCalls</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>그중 대체 모델(Claude)로 간 호출 수</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -9665,34 +10003,34 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>data.items[].inputTokens</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>입력 토큰</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>["항목","삼성전자","SK하이닉스"]</t>
+          <t>330000</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -9702,34 +10040,34 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>data.items[].outputTokens</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>출력 토큰(추론 토큰 포함)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>[["영업이익","...","..."]]</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -9739,34 +10077,34 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.items[].costUsd</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준(연결/별도)·미공시 표시</t>
+          <t>비용 추정(모델별 단가 × 토큰). 장부 금액 아님</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>0.0605</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -9776,34 +10114,34 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>data.detailId</t>
+          <t>data.items[].blocked</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID(분석 답변일 때)</t>
+          <t>관리자 정지 여부</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -9828,44 +10166,32 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ADMIN_ONLY</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>관리자 전용 API</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -9875,7 +10201,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Path detailId</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9890,34 +10216,34 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 ID</t>
+          <t>Bearer {JWT}(관리자)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dt_91c2...</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>data.report</t>
+          <t>Path memberId</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -9927,71 +10253,71 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 본문</t>
+          <t>대상 회원 ID</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>data.table.columns</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>String[]</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>표 머리글</t>
+          <t>true 정지 / false 해제</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>["항목", ...]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>data.table.rows</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>String[][]</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10001,19 +10327,19 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>표 행</t>
+          <t>사유(기록용)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>[[...]]</t>
+          <t>하루 한도를 반복해서 넘김</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -10023,59 +10349,71 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>data.table.note</t>
+          <t>data.memberId</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>재무제표 기준·미공시 표시</t>
+          <t>회원 ID</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>연결 기준</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="inlineStr"/>
+          <t>data.blocked</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr"/>
+          <t>바뀐 상태</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -10085,14 +10423,14 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>DETAIL_NOT_FOUND</t>
+          <t>AUTH_INVALID</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>상세 보기 대상 없음(또는 남의 것)</t>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
@@ -10100,81 +10438,57 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>ADMIN_ONLY</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Bearer eyJ...</t>
-        </is>
-      </c>
+          <t>관리자 전용 API</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>recipientAccountNumber</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>MEMBER_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>123456789012</t>
-        </is>
-      </c>
+          <t>회원 없음</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -10184,7 +10498,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -10194,24 +10508,24 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>엄마</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -10221,12 +10535,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>threadId</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -10236,29 +10550,29 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>대화 ID(체크포인터 키)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>th_5b21...</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>data.requestId</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -10273,19 +10587,19 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>송금 요청ID(1회용)</t>
+          <t>사용자 메시지</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>tr_7f3a...</t>
+          <t>엄마한테 1만원 보내줘</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -10295,7 +10609,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>data.recipientName</t>
+          <t>data.reply</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -10310,19 +10624,19 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>수취인 이름</t>
+          <t>요약 답변. 가드에 걸리면 고정 문장</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>삼성전자 2분기 영업이익은 ...</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -10332,7 +10646,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>data.recipientAccountNumber</t>
+          <t>data.guard</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -10347,19 +10661,19 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>수취인 계좌</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>123456789012</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -10369,7 +10683,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>data.fromAccountNumber</t>
+          <t>data.transferCard.requestId</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -10379,24 +10693,24 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌(대표 계좌)</t>
+          <t>송금 요청ID(1회용)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>987654321098</t>
+          <t>tr_7f3a...</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10406,34 +10720,34 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>data.amount</t>
+          <t>data.transferCard.recipientName</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
+          <t>수취인 이름</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>김영희</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -10443,7 +10757,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>data.expiresAt</t>
+          <t>data.transferCard.recipientAccountNumber</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -10453,183 +10767,219 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+          <t>수취인 계좌</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:05:00+09:00</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>AUTH_INVALID</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="inlineStr"/>
+          <t>data.transferCard.fromAccountNumber</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>JWT 없음·만료·위조, 로그인 실패</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
+          <t>출금 계좌(대표 계좌)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>987654321098</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>ALIAS_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="inlineStr"/>
+          <t>data.transferCard.amount</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>등록되지 않은 별칭</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>에러</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT_NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="2" t="inlineStr"/>
+          <t>data.transferCard.expiresAt</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>계좌 없음</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Header Authorization</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Bearer {JWT}</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Bearer eyJ...</t>
+          <t>["항목","삼성전자","SK하이닉스"]</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Query from</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>시작일(yyyy-MM-dd)</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>[["영업이익","...","..."]]</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Query to</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -10639,39 +10989,39 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>종료일(yyyy-MM-dd)</t>
+          <t>재무제표 기준(연결/별도)·미공시 표시</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>응답</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Query cursor</t>
+          <t>data.detailId</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -10681,67 +11031,59 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>E-09와 같은 커서 규칙</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr"/>
+          <t>상세 보기 ID(분석 답변일 때)</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>dt_91c2...</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Query size</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>기본 20</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>data.sentTotal</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -10751,34 +11093,34 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>data.receivedTotal</t>
+          <t>Path detailId</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10788,19 +11130,19 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>기간 내 받은 합계(원, Spring 계산)</t>
+          <t>상세 보기 ID</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>dt_91c2...</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -10810,12 +11152,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>data.count</t>
+          <t>data.report</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -10825,19 +11167,19 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>기간 내 건수</t>
+          <t>상세 보고서 본문</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -10847,34 +11189,34 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>data.items[].transferId</t>
+          <t>data.table.columns</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String[]</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>송금 ID</t>
+          <t>표 머리글</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>["항목", ...]</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -10884,34 +11226,34 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>data.items[].direction</t>
+          <t>data.table.rows</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String[][]</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>SENT / RECEIVED</t>
+          <t>표 행</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>[[...]]</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -10921,7 +11263,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartName</t>
+          <t>data.table.note</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -10931,108 +11273,84 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>상대 이름</t>
+          <t>재무제표 기준·미공시 표시</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>연결 기준</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>data.items[].counterpartAccountNumber</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>상대 계좌</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>123456789012</t>
-        </is>
-      </c>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>에러</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>data.items[].amount</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DETAIL_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>금액(원)</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
+          <t>상세 보기 대상 없음(또는 남의 것)</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>data.items[].createdAt</t>
+          <t>Header Authorization</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -11047,34 +11365,34 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>시각(ISO-8601)</t>
+          <t>Bearer {JWT}</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T10:01:00+09:00</t>
+          <t>Bearer eyJ...</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>data.nextCursor</t>
+          <t>recipientAccountNumber</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -11084,79 +11402,1001 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+          <t>수취인 계좌번호(alias와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>123456789012</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>응답</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>data.hasNext</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>다음 묶음 존재 여부</t>
+          <t>별칭(recipientAccountNumber와 둘 중 하나)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>엄마</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>data.requestId</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청ID(1회용)</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>tr_7f3a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>data.recipientName</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>수취인 이름</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>data.recipientAccountNumber</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>수취인 계좌</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>123456789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>data.fromAccountNumber</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>출금 계좌(대표 계좌)</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>987654321098</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>data.amount</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>data.expiresAt</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>만료 시각(생성 + 5분, ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:05:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>에러</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>AUTH_INVALID</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>JWT 없음·만료·위조, 로그인 실패</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>에러</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>ALIAS_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>등록되지 않은 별칭</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>에러</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>ACCOUNT_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>계좌 없음</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Header Authorization</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Bearer {JWT}</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Bearer eyJ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Query from</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>시작일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Query to</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>종료일(yyyy-MM-dd)</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Query cursor</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>E-09와 같은 커서 규칙</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Query size</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>기본 20</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>data.sentTotal</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 보낸 합계(원, Spring 계산)</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>data.receivedTotal</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 받은 합계(원, Spring 계산)</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>data.count</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>기간 내 건수</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].transferId</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>송금 ID</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].direction</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>SENT / RECEIVED</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].counterpartName</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>상대 이름</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].counterpartAccountNumber</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>상대 계좌</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>123456789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].amount</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>data.items[].createdAt</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>시각(ISO-8601)</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:01:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>data.nextCursor</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>다음 요청의 cursor(마지막 transferId). 없으면 null</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>data.hasNext</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>다음 묶음 존재 여부</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>에러</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>AUTH_INVALID</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>JWT 없음·만료·위조, 로그인 실패</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G184"/>
+  <autoFilter ref="A1:G210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>관리자 화면(JSP, 렌더링은 다른 화면처럼 인증 없이·데이터는 관리자 API): 날짜별 사용자 AI 사용량(LLM 호출 수·대체 호출 수·입력·출력 토큰·비용 추정, 많이 쓴 순)과 사용자별 AI 사용 정지·해제(사유 기록). 정지는 채팅·상세 보기만 막고 송금·계좌는 그대로(NFR-003과 같은 경계)</t>
+          <t>관리자 화면(/admin/ai-usage, JSP, 렌더링은 다른 화면처럼 인증 없이·데이터는 관리자 API): 날짜별 사용자 AI 사용량(LLM 호출 수·대체 호출 수·입력·출력 토큰·비용 추정, 많이 쓴 순, 정지된 회원은 사용이 없어도 포함)과 사용자별 AI 사용 정지·해제(사유 기록). 정지는 채팅·상세 보기만 막고 송금·계좌는 그대로(NFR-003과 같은 경계)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>많이 쓴 순. 날짜가 없으면 오늘(KST)</t>
+          <t>많이 쓴 순. 날짜가 없으면 오늘(KST). 정지된 회원은 그날 사용이 없어도 0으로 포함(화면에서 해제할 수 있게)</t>
         </is>
       </c>
     </row>

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>송금 확정 시 보낸 사람(출금)·받은 사람(입금)에게 알림. 알림 행은 확정 트랜잭션에 함께 저장((송금 ID, 받는 사람) 유일 키 — 커밋되면 반드시 남음), 커밋 뒤 접속 중인 사람에게 SSE로 보냄(확정 응답은 기다리지 않음). 놓친 알림은 목록으로. 화면은 Authorization 헤더를 붙이려고 EventSource 대신 fetch 스트림으로 받음(토큰을 URL에 넣지 않음). 서버 1대 기준이고 대량 전달은 NFR-045</t>
+          <t>송금 확정 시 보낸 사람(출금)·받은 사람(입금)에게 알림. 알림 행은 확정 트랜잭션에 함께 저장((송금 ID, 받는 사람) 유일 키 — 커밋되면 반드시 남음, 내 계좌끼리 보내면 받는 사람이 곧 보낸 사람이라 보낸 쪽 한 줄만), 커밋 뒤 접속 중인 사람에게 SSE로 보냄(확정 응답은 기다리지 않음). 놓친 알림은 목록으로. 화면은 Authorization 헤더를 붙이려고 EventSource 대신 fetch 스트림으로 받음(토큰을 URL에 넣지 않음). 서버 1대 기준이고 대량 전달은 NFR-045</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>도메인을 붙이고 nginx를 유일한 입구로: TLS 종료(Let's Encrypt, 자동 갱신), 80은 443으로 넘김, Spring으로 프록시(X-Forwarded-For·Proto 전달). 공유기는 80·443만 nginx로 넘기고 Spring 8080은 공개 중단(127.0.0.1에만). 타임아웃은 nginx &gt; Spring 읽기 제한(채팅 10초·상세 30초), 알림 스트림(E-15)은 버퍼링 끄고 하트비트 간격보다 길게. 로그인·가입은 IP별 요청 제한(limit_req). 부하 측정 환경은 지금처럼 Spring 직접(기준선 유지)</t>
+          <t>도메인을 붙이고 nginx를 유일한 입구로: TLS 종료(Let's Encrypt, 자동 갱신), 80은 443으로 넘김, Spring으로 프록시(X-Forwarded-For·Proto 전달). 공유기는 80·443만 nginx로 넘기고 Spring 8080은 공개 중단(127.0.0.1에만). 타임아웃은 nginx &gt; Spring 읽기 제한(채팅 10초·상세 30초), 알림 스트림(E-15)은 버퍼링 끄고 하트비트 간격보다 길게. 로그인·가입은 IP별 요청 제한(limit_req). 내부 경로(/internal/**·/actuator/**)는 입구에서 404. 부하 측정 환경은 지금처럼 Spring 직접(기준선 유지)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>사용자별 채팅 호출 제한 초과</t>
+          <t>호출 제한 초과 — 채팅은 사용자별(분당 10회), 로그인·가입은 IP별(nginx)</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -4331,7 +4331,11 @@
           <t>FR-001</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>입구(nginx)가 IP별로 제한한다(분당 10회, 연속 5회까지). 넘으면 429 RATE_LIMITED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4369,7 +4373,11 @@
           <t>FR-002</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>입구(nginx)가 IP별로 제한한다(분당 10회, 연속 5회까지). 넘으면 429 RATE_LIMITED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2498,15 +2498,19 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>간접 인젝션 검사</t>
+          <t>간접 인젝션 검사 — 사업의 내용 답변(공시 근거)에 외부 링크(URL·www·도메인 모양)나 비밀번호·OTP·PIN·인증번호·보안카드를 입력·전달하라는 문형이 있으면 guard=INDIRECT_INJECTION, 재검색 없이 고정 문장 + 출처. 일반 답변·상세 보고서에는 쓰지 않음. 인젝션 평가 세트 간접 범주로 차단율·오탐률 측정. 수집 때 지시문 탐지·LLM 판정은 추후</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>추후</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3637,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4252,95 +4256,71 @@
       <c r="G34" s="9" t="n"/>
       <c r="H34" s="10" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>INDIRECT_INJECTION</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>출력 교체 — 사업의 내용 답변의 외부 링크·비밀번호/인증번호 요구(공시 속 지시를 따른 흔적). 재검색 없이 고정 문장 + 출처</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>API ID</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>외부</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>/api/v1/auth/signup</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>회원가입</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>FR-001</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>입구(nginx)가 IP별로 제한한다(분당 10회, 연속 5회까지). 넘으면 429 RATE_LIMITED</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4355,12 +4335,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/signup</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>회원가입</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4370,7 +4350,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>FR-002</t>
+          <t>FR-001</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4382,7 +4362,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4397,34 +4377,34 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>가상계좌 개설</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Bearer</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>FR-003, FR-004</t>
+          <t>FR-002</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
+          <t>입구(nginx)가 IP별로 제한한다(분당 10회, 연속 5회까지). 넘으면 429 RATE_LIMITED</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4434,7 +4414,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4444,7 +4424,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>내 계좌·잔액 조회</t>
+          <t>가상계좌 개설</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -4454,15 +4434,19 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>FR-003, FR-004</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>첫 계좌면 대표. Idempotency-Key 헤더 필수 — 같은 키 재요청 시 새 계좌를 만들지 않고 기존 계좌를 반환</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4472,17 +4456,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/primary</t>
+          <t>/api/v1/accounts</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>대표 계좌 변경</t>
+          <t>내 계좌·잔액 조회</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -4492,7 +4476,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>FR-004</t>
+          <t>FR-006</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -4500,7 +4484,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4510,17 +4494,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/accounts/{accountId}/charge</t>
+          <t>/api/v1/accounts/{accountId}/primary</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>충전</t>
+          <t>대표 계좌 변경</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4530,7 +4514,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>FR-005</t>
+          <t>FR-004</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -4538,7 +4522,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4553,12 +4537,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/aliases</t>
+          <t>/api/v1/accounts/{accountId}/charge</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>별칭 등록</t>
+          <t>충전</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4568,7 +4552,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>FR-007</t>
+          <t>FR-005</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -4576,7 +4560,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -4586,7 +4570,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4596,7 +4580,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>별칭 목록</t>
+          <t>별칭 등록</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4606,7 +4590,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FR-008</t>
+          <t>FR-007</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -4614,7 +4598,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -4629,12 +4613,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfers?cursor&amp;size</t>
+          <t>/api/v1/aliases</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>송금 내역 목록</t>
+          <t>별칭 목록</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -4644,19 +4628,15 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>FR-011</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
-        </is>
-      </c>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4666,17 +4646,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads</t>
+          <t>/api/v1/transfers?cursor&amp;size</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>새 대화</t>
+          <t>송금 내역 목록</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4686,15 +4666,19 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FR-013</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>FR-011</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>최종 형태(커서). 개선 흐름: 전체 조회 → 오프셋 → 커서</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4709,12 +4693,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/threads/{threadId}/messages</t>
+          <t>/api/v1/chat/threads</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>채팅 메시지</t>
+          <t>새 대화</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4724,19 +4708,15 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024, NFR-054, NFR-055, NFR-056</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Spring이 I-01 호출. 호출 제한·AI 사용 정지·하루 한도 확인</t>
-        </is>
-      </c>
+          <t>FR-013</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4751,12 +4731,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
+          <t>/api/v1/chat/threads/{threadId}/messages</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>송금 확정([보내기])</t>
+          <t>채팅 메시지</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4766,19 +4746,19 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>FR-010, FR-024, NFR-001, NFR-009, NFR-010</t>
+          <t>FR-014, FR-015, FR-009, FR-012, FR-017, FR-018, FR-019, NFR-003, NFR-019, NFR-024, NFR-054, NFR-055, NFR-056</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음. 확정 트랜잭션에 알림 행 저장(FR-024)</t>
+          <t>Spring이 I-01 호출. 호출 제한·AI 사용 정지·하루 한도 확인</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4788,17 +4768,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/chat/details/{detailId}</t>
+          <t>/api/v1/transfer-requests/{requestId}/confirm</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>송금 확정([보내기])</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -4808,19 +4788,19 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>FR-016, FR-019, NFR-054, NFR-056</t>
+          <t>FR-010, FR-024, NFR-001, NFR-009, NFR-010</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Spring이 I-02 호출. AI 사용 정지·하루 한도 확인</t>
+          <t>AI 경로를 거치지 않음. 계좌 비밀번호도 여기서만 받음. 확정 트랜잭션에 알림 행 저장(FR-024)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4835,12 +4815,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/notifications?cursor&amp;size</t>
+          <t>/api/v1/chat/details/{detailId}</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4850,19 +4830,19 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>FR-024</t>
+          <t>FR-016, FR-019, NFR-054, NFR-056</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>최신순 커서(E-09와 같은 규칙). 스트림이 끊긴 사이 놓친 알림을 채움</t>
+          <t>Spring이 I-02 호출. AI 사용 정지·하루 한도 확인</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4877,12 +4857,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/stream</t>
+          <t>/api/v1/notifications?cursor&amp;size</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>알림 스트림(SSE)</t>
+          <t>알림 목록</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -4892,19 +4872,19 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>FR-024, NFR-053</t>
+          <t>FR-024</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>text/event-stream이라 응답 형식 공통 규칙의 예외. 화면은 fetch 스트림으로 받음(EventSource는 헤더를 못 붙임). 서버는 하트비트로 연결 유지</t>
+          <t>최신순 커서(E-09와 같은 규칙). 스트림이 끊긴 사이 놓친 알림을 채움</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4919,34 +4899,34 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/admin/ai-usage?date</t>
+          <t>/api/v1/notifications/stream</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>사용자별 AI 사용량</t>
+          <t>알림 스트림(SSE)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Bearer(관리자)</t>
+          <t>Bearer</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>FR-030, FR-031, NFR-054</t>
+          <t>FR-024, NFR-053</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>많이 쓴 순. 날짜가 없으면 오늘(KST). 정지된 회원은 그날 사용이 없어도 0으로 포함(화면에서 해제할 수 있게)</t>
+          <t>text/event-stream이라 응답 형식 공통 규칙의 예외. 화면은 fetch 스트림으로 받음(EventSource는 헤더를 못 붙임). 서버는 하트비트로 연결 유지</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4956,17 +4936,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/admin/members/{memberId}/ai-block</t>
+          <t>/api/v1/admin/ai-usage?date</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>AI 사용 정지·해제</t>
+          <t>사용자별 AI 사용량</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4976,61 +4956,61 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>FR-030, FR-031</t>
+          <t>FR-030, FR-031, NFR-054</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>다음 채팅부터 적용. 송금·계좌는 그대로</t>
+          <t>많이 쓴 순. 날짜가 없으면 오늘(KST). 정지된 회원은 그날 사용이 없어도 0으로 포함(화면에서 해제할 수 있게)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>내부 Spring→FastAPI</t>
+          <t>외부</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>/internal/chat</t>
+          <t>/api/v1/admin/members/{memberId}/ai-block</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>채팅 처리(LangGraph 구동)</t>
+          <t>AI 사용 정지·해제</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Bearer(사용자 JWT 전달)</t>
+          <t>Bearer(관리자)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>FR-014, FR-015, NFR-005, NFR-006, NFR-054, NFR-055, NFR-056</t>
+          <t>FR-030, FR-031</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API. 개인정보를 지우거나 가명화한 뒤 그래프에 넣고, LLM 호출마다 사용량 기록(사용자는 전달받은 JWT의 sub — Spring이 확인한 토큰)</t>
+          <t>다음 채팅부터 적용. 송금·계좌는 그대로</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -5040,17 +5020,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>/internal/details/{detailId}</t>
+          <t>/internal/chat</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>상세 보고서 생성</t>
+          <t>채팅 처리(LangGraph 구동)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -5060,39 +5040,39 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>FR-016, NFR-005, NFR-006, NFR-054, NFR-056</t>
+          <t>FR-014, FR-015, NFR-005, NFR-006, NFR-054, NFR-055, NFR-056</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>FastAPI 쪽 API. LLM 호출마다 사용량 기록</t>
+          <t>FastAPI 쪽 API. 개인정보를 지우거나 가명화한 뒤 그래프에 넣고, LLM 호출마다 사용량 기록(사용자는 전달받은 JWT의 sub — Spring이 확인한 토큰)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>내부 FastAPI→Spring</t>
+          <t>내부 Spring→FastAPI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>/internal/transfer-requests</t>
+          <t>/internal/details/{detailId}</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>송금 요청 생성(확인 카드용)</t>
+          <t>상세 보고서 생성</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -5102,60 +5082,103 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>FR-009, NFR-001, NFR-005, NFR-006, NFR-055</t>
+          <t>FR-016, NFR-005, NFR-006, NFR-054, NFR-056</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>LangGraph 도구. 실행은 하지 않음. 가명화한 계좌번호([계좌1])는 부르기 직전에 원래 번호로 되돌림</t>
+          <t>FastAPI 쪽 API. LLM 호출마다 사용량 기록</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>내부 FastAPI→Spring</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>/internal/transfer-requests</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>송금 요청 생성(확인 카드용)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Bearer(사용자 JWT 전달)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>FR-009, NFR-001, NFR-005, NFR-006, NFR-055</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph 도구. 실행은 하지 않음. 가명화한 계좌번호([계좌1])는 부르기 직전에 원래 번호로 되돌림</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>내부 FastAPI→Spring</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>/internal/transfers?from&amp;to&amp;cursor&amp;size</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>송금 내역·합계 조회</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Bearer(사용자 JWT 전달)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>FR-012, NFR-002, NFR-005, NFR-006</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>LangGraph 도구. 합계는 Spring 계산</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A36:H57"/>
-  <mergeCells count="34">
+  <autoFilter ref="A37:H58"/>
+  <mergeCells count="35">
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="C22:H22"/>
@@ -7787,7 +7810,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK / INDIRECT_INJECTION</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -10669,7 +10692,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK</t>
+          <t>판정 코드: PASS / INJECTION / NUMBER_UNVERIFIED / ADVICE / PROMPT_LEAK / INDIRECT_INJECTION</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
+          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 판정 전 입력 정규화(NFKC·보이지 않는 서식 문자 제거, 판정에만 쓰고 LLM·기록에는 원래 글). 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 판정 전 입력 정규화(NFKC·보이지 않는 서식 문자 제거, 판정에만 쓰고 LLM·기록에는 원래 글). 공격 세트로 차단율, 정상 세트로 오탐률 측정</t>
+          <t>대표 유형 규칙으로 판정 → guard=INJECTION, LLM 미호출, 고정 문장. 판정 전 입력 정규화(NFKC·보이지 않는 서식 문자 제거, 판정에만 쓰고 LLM·기록에는 원래 글). 공격 세트로 차단율, 정상 세트로 오탐률 측정. CI에서 기준치 회귀(지금 수치보다 나빠지면 실패, 간접 범주 포함)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>NFR-013(주민·카드번호 가림)을 넓힘. LLM이 값을 알아야 하는지로 나눔: 필요 없음(주민·카드·전화번호·이메일) → 제거(자리표시자로 바꾸고 되돌리지 않음). 가리켜야 함(수취인 계좌번호) → 가명화([계좌1]로 보내고 송금 요청 도구 직전에 코드가 되돌림, 대응표는 서버의 대화 상태에만). 탐지가 어려움(실명) → 구조로 피함(송금은 별칭·계좌번호로만 받고, 코드가 만든 답변(확인 문장·내역)의 실명은 대화 기록에 자리표시자로 남겨 다음 LLM 호출에 안 실림). 개인정보 문장 세트로 LLM에 간 원문 0건·오탐률, 송금 발화 세트(NFR-014) 일치율 유지 확인</t>
+          <t>NFR-013(주민·카드번호 가림)을 넓힘. LLM이 값을 알아야 하는지로 나눔: 필요 없음(주민·카드·전화번호·이메일, 비밀번호·OTP·인증번호 낱말 옆 4~8자리 숫자) → 제거(자리표시자로 바꾸고 되돌리지 않음). 가리켜야 함(수취인 계좌번호) → 가명화([계좌1]로 보내고 송금 요청 도구 직전에 코드가 되돌림, 대응표는 서버의 대화 상태에만). 탐지가 어려움(실명) → 구조로 피함(송금은 별칭·계좌번호로만 받고, 코드가 만든 답변(확인 문장·내역)의 실명은 대화 기록에 자리표시자로 남겨 다음 LLM 호출에 안 실림). 개인정보 문장 세트로 LLM에 간 원문 0건·오탐률, 송금 발화 세트(NFR-014) 일치율 유지 확인</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">

--- a/docs/smart-spec.xlsx
+++ b/docs/smart-spec.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK</t>
+          <t>프롬프트에 카나리 단어를 심고 답변에 나오면 guard=PROMPT_LEAK. 또는 답변이 프롬프트 5개(일반·의도 추출·사업의 내용·재검색·상세 보고서) 중 하나와 공백·기호를 뺀 20자 이상 겹치면 PROMPT_LEAK(번역·요약 유출은 추후 LLM 판정). 추출한 기업 이름이 30자를 넘으면 쓰지 않음(코드 답변에 되풀이 방지, LLM05). 인젝션 평가 세트 유출 범주로 측정</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
